--- a/AAII_Financials/Yearly/DOYU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOYU_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -721,25 +721,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>981500</v>
+        <v>988200</v>
       </c>
       <c r="E8" s="3">
-        <v>1265500</v>
+        <v>1274200</v>
       </c>
       <c r="F8" s="3">
-        <v>1325800</v>
+        <v>1334900</v>
       </c>
       <c r="G8" s="3">
-        <v>1005700</v>
+        <v>1012500</v>
       </c>
       <c r="H8" s="3">
-        <v>504600</v>
+        <v>508000</v>
       </c>
       <c r="I8" s="3">
-        <v>260400</v>
+        <v>262200</v>
       </c>
       <c r="J8" s="3">
-        <v>108600</v>
+        <v>109400</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -760,25 +760,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>844800</v>
+        <v>850500</v>
       </c>
       <c r="E9" s="3">
-        <v>1115100</v>
+        <v>1122600</v>
       </c>
       <c r="F9" s="3">
-        <v>1110400</v>
+        <v>1117900</v>
       </c>
       <c r="G9" s="3">
-        <v>840500</v>
+        <v>846200</v>
       </c>
       <c r="H9" s="3">
-        <v>483700</v>
+        <v>487000</v>
       </c>
       <c r="I9" s="3">
-        <v>261000</v>
+        <v>262800</v>
       </c>
       <c r="J9" s="3">
-        <v>159500</v>
+        <v>160600</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -799,25 +799,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>136700</v>
+        <v>137600</v>
       </c>
       <c r="E10" s="3">
-        <v>150500</v>
+        <v>151500</v>
       </c>
       <c r="F10" s="3">
-        <v>215500</v>
+        <v>216900</v>
       </c>
       <c r="G10" s="3">
-        <v>165200</v>
+        <v>166300</v>
       </c>
       <c r="H10" s="3">
-        <v>20900</v>
+        <v>21000</v>
       </c>
       <c r="I10" s="3">
         <v>-600</v>
       </c>
       <c r="J10" s="3">
-        <v>-50800</v>
+        <v>-51200</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -855,25 +855,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>52900</v>
+        <v>53300</v>
       </c>
       <c r="E12" s="3">
-        <v>67700</v>
+        <v>68100</v>
       </c>
       <c r="F12" s="3">
-        <v>57500</v>
+        <v>57900</v>
       </c>
       <c r="G12" s="3">
-        <v>53000</v>
+        <v>53400</v>
       </c>
       <c r="H12" s="3">
-        <v>45500</v>
+        <v>45800</v>
       </c>
       <c r="I12" s="3">
-        <v>29300</v>
+        <v>29500</v>
       </c>
       <c r="J12" s="3">
-        <v>12900</v>
+        <v>13000</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>-3200</v>
+        <v>-3300</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -1025,25 +1025,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1009000</v>
+        <v>1015800</v>
       </c>
       <c r="E17" s="3">
-        <v>1355100</v>
+        <v>1364300</v>
       </c>
       <c r="F17" s="3">
-        <v>1286400</v>
+        <v>1295200</v>
       </c>
       <c r="G17" s="3">
-        <v>1023800</v>
+        <v>1030800</v>
       </c>
       <c r="H17" s="3">
-        <v>623200</v>
+        <v>627500</v>
       </c>
       <c r="I17" s="3">
-        <v>345800</v>
+        <v>348100</v>
       </c>
       <c r="J17" s="3">
-        <v>215900</v>
+        <v>217300</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1064,25 +1064,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-27500</v>
+        <v>-27600</v>
       </c>
       <c r="E18" s="3">
-        <v>-89600</v>
+        <v>-90200</v>
       </c>
       <c r="F18" s="3">
-        <v>39400</v>
+        <v>39700</v>
       </c>
       <c r="G18" s="3">
-        <v>-18200</v>
+        <v>-18300</v>
       </c>
       <c r="H18" s="3">
-        <v>-118600</v>
+        <v>-119400</v>
       </c>
       <c r="I18" s="3">
-        <v>-85400</v>
+        <v>-86000</v>
       </c>
       <c r="J18" s="3">
-        <v>-107200</v>
+        <v>-107900</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1120,16 +1120,16 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>6800</v>
+        <v>6900</v>
       </c>
       <c r="E20" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="F20" s="3">
-        <v>16300</v>
+        <v>16400</v>
       </c>
       <c r="G20" s="3">
-        <v>23200</v>
+        <v>23400</v>
       </c>
       <c r="H20" s="3">
         <v>-1400</v>
@@ -1159,25 +1159,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-8500</v>
+        <v>-8600</v>
       </c>
       <c r="E21" s="3">
-        <v>-71300</v>
+        <v>-71800</v>
       </c>
       <c r="F21" s="3">
-        <v>71000</v>
+        <v>71500</v>
       </c>
       <c r="G21" s="3">
-        <v>17500</v>
+        <v>17600</v>
       </c>
       <c r="H21" s="3">
-        <v>-113700</v>
+        <v>-114500</v>
       </c>
       <c r="I21" s="3">
-        <v>-80900</v>
+        <v>-81400</v>
       </c>
       <c r="J21" s="3">
-        <v>-105600</v>
+        <v>-106300</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1237,25 +1237,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-20600</v>
+        <v>-20800</v>
       </c>
       <c r="E23" s="3">
-        <v>-83600</v>
+        <v>-84100</v>
       </c>
       <c r="F23" s="3">
-        <v>55700</v>
+        <v>56100</v>
       </c>
       <c r="G23" s="3">
         <v>5100</v>
       </c>
       <c r="H23" s="3">
-        <v>-120000</v>
+        <v>-120800</v>
       </c>
       <c r="I23" s="3">
-        <v>-84500</v>
+        <v>-85000</v>
       </c>
       <c r="J23" s="3">
-        <v>-107800</v>
+        <v>-108500</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1354,25 +1354,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-21100</v>
+        <v>-21200</v>
       </c>
       <c r="E26" s="3">
-        <v>-83600</v>
+        <v>-84100</v>
       </c>
       <c r="F26" s="3">
-        <v>55700</v>
+        <v>56100</v>
       </c>
       <c r="G26" s="3">
         <v>5100</v>
       </c>
       <c r="H26" s="3">
-        <v>-120000</v>
+        <v>-120800</v>
       </c>
       <c r="I26" s="3">
-        <v>-84500</v>
+        <v>-85000</v>
       </c>
       <c r="J26" s="3">
-        <v>-107800</v>
+        <v>-108500</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1393,25 +1393,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-10400</v>
+        <v>-10500</v>
       </c>
       <c r="E27" s="3">
-        <v>-80300</v>
+        <v>-80900</v>
       </c>
       <c r="F27" s="3">
-        <v>67000</v>
+        <v>67500</v>
       </c>
       <c r="G27" s="3">
         <v>5500</v>
       </c>
       <c r="H27" s="3">
-        <v>-121900</v>
+        <v>-122700</v>
       </c>
       <c r="I27" s="3">
-        <v>-84600</v>
+        <v>-85200</v>
       </c>
       <c r="J27" s="3">
-        <v>-147400</v>
+        <v>-148500</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1588,16 +1588,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6800</v>
+        <v>-6900</v>
       </c>
       <c r="E32" s="3">
-        <v>-6000</v>
+        <v>-6100</v>
       </c>
       <c r="F32" s="3">
-        <v>-16300</v>
+        <v>-16400</v>
       </c>
       <c r="G32" s="3">
-        <v>-23200</v>
+        <v>-23400</v>
       </c>
       <c r="H32" s="3">
         <v>1400</v>
@@ -1627,25 +1627,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-10400</v>
+        <v>-10500</v>
       </c>
       <c r="E33" s="3">
-        <v>-80300</v>
+        <v>-80900</v>
       </c>
       <c r="F33" s="3">
-        <v>67000</v>
+        <v>67500</v>
       </c>
       <c r="G33" s="3">
         <v>5500</v>
       </c>
       <c r="H33" s="3">
-        <v>-121900</v>
+        <v>-122700</v>
       </c>
       <c r="I33" s="3">
-        <v>-84600</v>
+        <v>-85200</v>
       </c>
       <c r="J33" s="3">
-        <v>-147400</v>
+        <v>-148500</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1705,25 +1705,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-10400</v>
+        <v>-10500</v>
       </c>
       <c r="E35" s="3">
-        <v>-80300</v>
+        <v>-80900</v>
       </c>
       <c r="F35" s="3">
-        <v>67000</v>
+        <v>67500</v>
       </c>
       <c r="G35" s="3">
         <v>5500</v>
       </c>
       <c r="H35" s="3">
-        <v>-121900</v>
+        <v>-122700</v>
       </c>
       <c r="I35" s="3">
-        <v>-84600</v>
+        <v>-85200</v>
       </c>
       <c r="J35" s="3">
-        <v>-147400</v>
+        <v>-148500</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1822,25 +1822,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>558100</v>
+        <v>561900</v>
       </c>
       <c r="E41" s="3">
-        <v>615300</v>
+        <v>619500</v>
       </c>
       <c r="F41" s="3">
-        <v>729000</v>
+        <v>734000</v>
       </c>
       <c r="G41" s="3">
-        <v>1117300</v>
+        <v>1124900</v>
       </c>
       <c r="H41" s="3">
-        <v>768000</v>
+        <v>773300</v>
       </c>
       <c r="I41" s="3">
-        <v>74500</v>
+        <v>75000</v>
       </c>
       <c r="J41" s="3">
-        <v>71400</v>
+        <v>71800</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1861,13 +1861,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>346700</v>
+        <v>349100</v>
       </c>
       <c r="E42" s="3">
-        <v>286700</v>
+        <v>288700</v>
       </c>
       <c r="F42" s="3">
-        <v>308000</v>
+        <v>310000</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
@@ -1900,25 +1900,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>64300</v>
+        <v>64700</v>
       </c>
       <c r="E43" s="3">
-        <v>75800</v>
+        <v>76300</v>
       </c>
       <c r="F43" s="3">
-        <v>58000</v>
+        <v>58400</v>
       </c>
       <c r="G43" s="3">
-        <v>54800</v>
+        <v>55200</v>
       </c>
       <c r="H43" s="3">
-        <v>52800</v>
+        <v>53200</v>
       </c>
       <c r="I43" s="3">
-        <v>32100</v>
+        <v>32300</v>
       </c>
       <c r="J43" s="3">
-        <v>16200</v>
+        <v>16300</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1978,22 +1978,22 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>8100</v>
+        <v>8200</v>
       </c>
       <c r="E45" s="3">
-        <v>20400</v>
+        <v>20500</v>
       </c>
       <c r="F45" s="3">
-        <v>14300</v>
+        <v>14400</v>
       </c>
       <c r="G45" s="3">
-        <v>15500</v>
+        <v>15600</v>
       </c>
       <c r="H45" s="3">
-        <v>23800</v>
+        <v>24000</v>
       </c>
       <c r="I45" s="3">
-        <v>12600</v>
+        <v>12700</v>
       </c>
       <c r="J45" s="3">
         <v>5800</v>
@@ -2017,25 +2017,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>977200</v>
+        <v>983900</v>
       </c>
       <c r="E46" s="3">
-        <v>998200</v>
+        <v>1005000</v>
       </c>
       <c r="F46" s="3">
-        <v>1109300</v>
+        <v>1116900</v>
       </c>
       <c r="G46" s="3">
-        <v>1187700</v>
+        <v>1195800</v>
       </c>
       <c r="H46" s="3">
-        <v>844600</v>
+        <v>850400</v>
       </c>
       <c r="I46" s="3">
-        <v>119100</v>
+        <v>120000</v>
       </c>
       <c r="J46" s="3">
-        <v>93300</v>
+        <v>94000</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2056,25 +2056,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>108000</v>
+        <v>108700</v>
       </c>
       <c r="E47" s="3">
-        <v>81700</v>
+        <v>82200</v>
       </c>
       <c r="F47" s="3">
-        <v>82900</v>
+        <v>83500</v>
       </c>
       <c r="G47" s="3">
-        <v>31100</v>
+        <v>31400</v>
       </c>
       <c r="H47" s="3">
-        <v>18500</v>
+        <v>18700</v>
       </c>
       <c r="I47" s="3">
-        <v>13300</v>
+        <v>13400</v>
       </c>
       <c r="J47" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -2095,13 +2095,13 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>9200</v>
+        <v>9300</v>
       </c>
       <c r="E48" s="3">
         <v>13500</v>
       </c>
       <c r="F48" s="3">
-        <v>13800</v>
+        <v>13900</v>
       </c>
       <c r="G48" s="3">
         <v>5400</v>
@@ -2110,10 +2110,10 @@
         <v>7000</v>
       </c>
       <c r="I48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J48" s="3">
         <v>6900</v>
-      </c>
-      <c r="J48" s="3">
-        <v>6800</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2134,19 +2134,19 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>16600</v>
+        <v>16800</v>
       </c>
       <c r="E49" s="3">
-        <v>24100</v>
+        <v>24200</v>
       </c>
       <c r="F49" s="3">
-        <v>21300</v>
+        <v>21500</v>
       </c>
       <c r="G49" s="3">
-        <v>31600</v>
+        <v>31800</v>
       </c>
       <c r="H49" s="3">
-        <v>20000</v>
+        <v>20100</v>
       </c>
       <c r="I49" s="3">
         <v>2300</v>
@@ -2251,10 +2251,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>13600</v>
+        <v>13700</v>
       </c>
       <c r="E52" s="3">
-        <v>8900</v>
+        <v>9000</v>
       </c>
       <c r="F52" s="3">
         <v>2600</v>
@@ -2263,7 +2263,7 @@
         <v>1200</v>
       </c>
       <c r="H52" s="3">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="I52" s="3">
         <v>800</v>
@@ -2329,25 +2329,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1124700</v>
+        <v>1132400</v>
       </c>
       <c r="E54" s="3">
-        <v>1126300</v>
+        <v>1134000</v>
       </c>
       <c r="F54" s="3">
-        <v>1230000</v>
+        <v>1238400</v>
       </c>
       <c r="G54" s="3">
-        <v>1257000</v>
+        <v>1265600</v>
       </c>
       <c r="H54" s="3">
-        <v>896800</v>
+        <v>902900</v>
       </c>
       <c r="I54" s="3">
-        <v>142400</v>
+        <v>143400</v>
       </c>
       <c r="J54" s="3">
-        <v>107600</v>
+        <v>108300</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2402,25 +2402,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>92100</v>
+        <v>92700</v>
       </c>
       <c r="E57" s="3">
-        <v>113800</v>
+        <v>114600</v>
       </c>
       <c r="F57" s="3">
-        <v>136200</v>
+        <v>137100</v>
       </c>
       <c r="G57" s="3">
-        <v>122900</v>
+        <v>123700</v>
       </c>
       <c r="H57" s="3">
-        <v>110500</v>
+        <v>111300</v>
       </c>
       <c r="I57" s="3">
-        <v>62400</v>
+        <v>62800</v>
       </c>
       <c r="J57" s="3">
-        <v>46400</v>
+        <v>46700</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2480,25 +2480,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>123100</v>
+        <v>124000</v>
       </c>
       <c r="E59" s="3">
-        <v>141500</v>
+        <v>142500</v>
       </c>
       <c r="F59" s="3">
-        <v>123800</v>
+        <v>124700</v>
       </c>
       <c r="G59" s="3">
-        <v>124900</v>
+        <v>125700</v>
       </c>
       <c r="H59" s="3">
-        <v>284900</v>
+        <v>286900</v>
       </c>
       <c r="I59" s="3">
-        <v>58000</v>
+        <v>58400</v>
       </c>
       <c r="J59" s="3">
-        <v>25900</v>
+        <v>26100</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2519,25 +2519,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>215200</v>
+        <v>216700</v>
       </c>
       <c r="E60" s="3">
-        <v>255300</v>
+        <v>257000</v>
       </c>
       <c r="F60" s="3">
-        <v>260000</v>
+        <v>261800</v>
       </c>
       <c r="G60" s="3">
-        <v>247700</v>
+        <v>249400</v>
       </c>
       <c r="H60" s="3">
-        <v>395400</v>
+        <v>398100</v>
       </c>
       <c r="I60" s="3">
-        <v>120400</v>
+        <v>121200</v>
       </c>
       <c r="J60" s="3">
-        <v>72300</v>
+        <v>72800</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2600,7 +2600,7 @@
         <v>3600</v>
       </c>
       <c r="E62" s="3">
-        <v>6800</v>
+        <v>6900</v>
       </c>
       <c r="F62" s="3">
         <v>6600</v>
@@ -2753,25 +2753,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>218800</v>
+        <v>220300</v>
       </c>
       <c r="E66" s="3">
-        <v>262100</v>
+        <v>263900</v>
       </c>
       <c r="F66" s="3">
-        <v>271900</v>
+        <v>273700</v>
       </c>
       <c r="G66" s="3">
-        <v>257100</v>
+        <v>258800</v>
       </c>
       <c r="H66" s="3">
-        <v>395400</v>
+        <v>398100</v>
       </c>
       <c r="I66" s="3">
-        <v>120400</v>
+        <v>121200</v>
       </c>
       <c r="J66" s="3">
-        <v>72300</v>
+        <v>72800</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2899,13 +2899,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>917500</v>
+        <v>923800</v>
       </c>
       <c r="I70" s="3">
-        <v>363100</v>
+        <v>365500</v>
       </c>
       <c r="J70" s="3">
-        <v>294000</v>
+        <v>296000</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -2965,25 +2965,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-486100</v>
+        <v>-489400</v>
       </c>
       <c r="E72" s="3">
-        <v>-475700</v>
+        <v>-478900</v>
       </c>
       <c r="F72" s="3">
-        <v>-395400</v>
+        <v>-398000</v>
       </c>
       <c r="G72" s="3">
-        <v>-462400</v>
+        <v>-465500</v>
       </c>
       <c r="H72" s="3">
-        <v>-467900</v>
+        <v>-471100</v>
       </c>
       <c r="I72" s="3">
-        <v>-346900</v>
+        <v>-349200</v>
       </c>
       <c r="J72" s="3">
-        <v>-262300</v>
+        <v>-264000</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3121,25 +3121,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>905900</v>
+        <v>912000</v>
       </c>
       <c r="E76" s="3">
-        <v>864200</v>
+        <v>870100</v>
       </c>
       <c r="F76" s="3">
-        <v>958100</v>
+        <v>964700</v>
       </c>
       <c r="G76" s="3">
-        <v>1000000</v>
+        <v>1006800</v>
       </c>
       <c r="H76" s="3">
-        <v>-416100</v>
+        <v>-419000</v>
       </c>
       <c r="I76" s="3">
-        <v>-341000</v>
+        <v>-343300</v>
       </c>
       <c r="J76" s="3">
-        <v>-258800</v>
+        <v>-260500</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3243,25 +3243,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-10400</v>
+        <v>-10500</v>
       </c>
       <c r="E81" s="3">
-        <v>-80300</v>
+        <v>-80900</v>
       </c>
       <c r="F81" s="3">
-        <v>67000</v>
+        <v>67500</v>
       </c>
       <c r="G81" s="3">
         <v>5500</v>
       </c>
       <c r="H81" s="3">
-        <v>-121900</v>
+        <v>-122700</v>
       </c>
       <c r="I81" s="3">
-        <v>-84600</v>
+        <v>-85200</v>
       </c>
       <c r="J81" s="3">
-        <v>-147400</v>
+        <v>-148500</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3299,16 +3299,16 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12100</v>
+        <v>12200</v>
       </c>
       <c r="E83" s="3">
         <v>12300</v>
       </c>
       <c r="F83" s="3">
-        <v>15300</v>
+        <v>15400</v>
       </c>
       <c r="G83" s="3">
-        <v>12400</v>
+        <v>12500</v>
       </c>
       <c r="H83" s="3">
         <v>6300</v>
@@ -3536,22 +3536,22 @@
         <v>-9400</v>
       </c>
       <c r="E89" s="3">
-        <v>-81000</v>
+        <v>-81500</v>
       </c>
       <c r="F89" s="3">
-        <v>92200</v>
+        <v>92800</v>
       </c>
       <c r="G89" s="3">
-        <v>112300</v>
+        <v>113000</v>
       </c>
       <c r="H89" s="3">
-        <v>-46600</v>
+        <v>-46900</v>
       </c>
       <c r="I89" s="3">
-        <v>-52600</v>
+        <v>-53000</v>
       </c>
       <c r="J89" s="3">
-        <v>-98600</v>
+        <v>-99300</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3592,16 +3592,16 @@
         <v>-800</v>
       </c>
       <c r="E91" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="F91" s="3">
-        <v>-2600</v>
+        <v>-2700</v>
       </c>
       <c r="G91" s="3">
         <v>-2200</v>
       </c>
       <c r="H91" s="3">
-        <v>-4500</v>
+        <v>-4600</v>
       </c>
       <c r="I91" s="3">
         <v>-3300</v>
@@ -3706,25 +3706,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-84000</v>
+        <v>-84600</v>
       </c>
       <c r="E94" s="3">
-        <v>-2600</v>
+        <v>-2700</v>
       </c>
       <c r="F94" s="3">
-        <v>-360800</v>
+        <v>-363200</v>
       </c>
       <c r="G94" s="3">
-        <v>-34000</v>
+        <v>-34200</v>
       </c>
       <c r="H94" s="3">
-        <v>-36600</v>
+        <v>-36800</v>
       </c>
       <c r="I94" s="3">
-        <v>-12700</v>
+        <v>-12800</v>
       </c>
       <c r="J94" s="3">
-        <v>-11900</v>
+        <v>-12000</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3918,25 +3918,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-15000</v>
+        <v>-15100</v>
       </c>
       <c r="E100" s="3">
-        <v>-14800</v>
+        <v>-14900</v>
       </c>
       <c r="F100" s="3">
-        <v>-66200</v>
+        <v>-66600</v>
       </c>
       <c r="G100" s="3">
-        <v>261800</v>
+        <v>263600</v>
       </c>
       <c r="H100" s="3">
-        <v>729100</v>
+        <v>734000</v>
       </c>
       <c r="I100" s="3">
-        <v>69000</v>
+        <v>69500</v>
       </c>
       <c r="J100" s="3">
-        <v>179300</v>
+        <v>180500</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3957,19 +3957,19 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>50500</v>
+        <v>50900</v>
       </c>
       <c r="E101" s="3">
-        <v>-15500</v>
+        <v>-15600</v>
       </c>
       <c r="F101" s="3">
-        <v>-57800</v>
+        <v>-58200</v>
       </c>
       <c r="G101" s="3">
-        <v>15100</v>
+        <v>15200</v>
       </c>
       <c r="H101" s="3">
-        <v>47600</v>
+        <v>48000</v>
       </c>
       <c r="I101" s="3">
         <v>-600</v>
@@ -3996,25 +3996,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-57900</v>
+        <v>-58300</v>
       </c>
       <c r="E102" s="3">
-        <v>-113900</v>
+        <v>-114600</v>
       </c>
       <c r="F102" s="3">
-        <v>-392600</v>
+        <v>-395200</v>
       </c>
       <c r="G102" s="3">
-        <v>355200</v>
+        <v>357700</v>
       </c>
       <c r="H102" s="3">
-        <v>693500</v>
+        <v>698200</v>
       </c>
       <c r="I102" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="J102" s="3">
-        <v>68900</v>
+        <v>69400</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/DOYU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOYU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
   <si>
     <t>DOYU</t>
   </si>
@@ -656,55 +656,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -714,36 +714,39 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>988200</v>
+        <v>764100</v>
       </c>
       <c r="E8" s="3">
-        <v>1274200</v>
+        <v>982100</v>
       </c>
       <c r="F8" s="3">
-        <v>1334900</v>
+        <v>1266300</v>
       </c>
       <c r="G8" s="3">
-        <v>1012500</v>
+        <v>1326600</v>
       </c>
       <c r="H8" s="3">
-        <v>508000</v>
+        <v>1006300</v>
       </c>
       <c r="I8" s="3">
-        <v>262200</v>
+        <v>504900</v>
       </c>
       <c r="J8" s="3">
+        <v>260500</v>
+      </c>
+      <c r="K8" s="3">
         <v>109400</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -753,36 +756,39 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>850500</v>
+        <v>669600</v>
       </c>
       <c r="E9" s="3">
-        <v>1122600</v>
+        <v>845300</v>
       </c>
       <c r="F9" s="3">
-        <v>1117900</v>
+        <v>1115700</v>
       </c>
       <c r="G9" s="3">
-        <v>846200</v>
+        <v>1111000</v>
       </c>
       <c r="H9" s="3">
-        <v>487000</v>
+        <v>841000</v>
       </c>
       <c r="I9" s="3">
-        <v>262800</v>
+        <v>484000</v>
       </c>
       <c r="J9" s="3">
+        <v>261200</v>
+      </c>
+      <c r="K9" s="3">
         <v>160600</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -792,36 +798,39 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>137600</v>
+        <v>94500</v>
       </c>
       <c r="E10" s="3">
-        <v>151500</v>
+        <v>136800</v>
       </c>
       <c r="F10" s="3">
-        <v>216900</v>
+        <v>150600</v>
       </c>
       <c r="G10" s="3">
-        <v>166300</v>
+        <v>215600</v>
       </c>
       <c r="H10" s="3">
-        <v>21000</v>
+        <v>165300</v>
       </c>
       <c r="I10" s="3">
+        <v>20900</v>
+      </c>
+      <c r="J10" s="3">
         <v>-600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-51200</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,9 +840,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,35 +861,36 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>53300</v>
+        <v>38300</v>
       </c>
       <c r="E12" s="3">
-        <v>68100</v>
+        <v>52900</v>
       </c>
       <c r="F12" s="3">
-        <v>57900</v>
+        <v>67700</v>
       </c>
       <c r="G12" s="3">
-        <v>53400</v>
+        <v>57500</v>
       </c>
       <c r="H12" s="3">
-        <v>45800</v>
+        <v>53000</v>
       </c>
       <c r="I12" s="3">
-        <v>29500</v>
+        <v>45500</v>
       </c>
       <c r="J12" s="3">
+        <v>29300</v>
+      </c>
+      <c r="K12" s="3">
         <v>13000</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -887,9 +900,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,35 +942,38 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-3300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>-3200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-900</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
@@ -965,9 +984,12 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1004,9 +1026,12 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1019,35 +1044,36 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1015800</v>
+        <v>786700</v>
       </c>
       <c r="E17" s="3">
-        <v>1364300</v>
+        <v>1009600</v>
       </c>
       <c r="F17" s="3">
-        <v>1295200</v>
+        <v>1355900</v>
       </c>
       <c r="G17" s="3">
-        <v>1030800</v>
+        <v>1287100</v>
       </c>
       <c r="H17" s="3">
-        <v>627500</v>
+        <v>1024400</v>
       </c>
       <c r="I17" s="3">
-        <v>348100</v>
+        <v>623600</v>
       </c>
       <c r="J17" s="3">
+        <v>346000</v>
+      </c>
+      <c r="K17" s="3">
         <v>217300</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1057,36 +1083,39 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-27600</v>
+        <v>-22700</v>
       </c>
       <c r="E18" s="3">
-        <v>-90200</v>
+        <v>-27500</v>
       </c>
       <c r="F18" s="3">
-        <v>39700</v>
+        <v>-89600</v>
       </c>
       <c r="G18" s="3">
-        <v>-18300</v>
+        <v>39500</v>
       </c>
       <c r="H18" s="3">
-        <v>-119400</v>
+        <v>-18200</v>
       </c>
       <c r="I18" s="3">
-        <v>-86000</v>
+        <v>-118700</v>
       </c>
       <c r="J18" s="3">
+        <v>-85400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-107900</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1096,9 +1125,12 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1114,35 +1146,36 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>6900</v>
+        <v>32100</v>
       </c>
       <c r="E20" s="3">
-        <v>6100</v>
+        <v>6800</v>
       </c>
       <c r="F20" s="3">
-        <v>16400</v>
+        <v>6000</v>
       </c>
       <c r="G20" s="3">
-        <v>23400</v>
+        <v>16300</v>
       </c>
       <c r="H20" s="3">
+        <v>23200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1152,36 +1185,39 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8600</v>
       </c>
-      <c r="E21" s="3">
-        <v>-71800</v>
-      </c>
       <c r="F21" s="3">
-        <v>71500</v>
+        <v>-71400</v>
       </c>
       <c r="G21" s="3">
-        <v>17600</v>
+        <v>71000</v>
       </c>
       <c r="H21" s="3">
-        <v>-114500</v>
+        <v>17500</v>
       </c>
       <c r="I21" s="3">
-        <v>-81400</v>
+        <v>-113800</v>
       </c>
       <c r="J21" s="3">
+        <v>-80900</v>
+      </c>
+      <c r="K21" s="3">
         <v>-106300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1191,9 +1227,12 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1209,18 +1248,18 @@
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>1200</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,36 +1269,39 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-20800</v>
+        <v>9400</v>
       </c>
       <c r="E23" s="3">
-        <v>-84100</v>
+        <v>-20600</v>
       </c>
       <c r="F23" s="3">
-        <v>56100</v>
+        <v>-83600</v>
       </c>
       <c r="G23" s="3">
+        <v>55700</v>
+      </c>
+      <c r="H23" s="3">
         <v>5100</v>
       </c>
-      <c r="H23" s="3">
-        <v>-120800</v>
-      </c>
       <c r="I23" s="3">
-        <v>-85000</v>
+        <v>-120100</v>
       </c>
       <c r="J23" s="3">
+        <v>-84500</v>
+      </c>
+      <c r="K23" s="3">
         <v>-108500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,23 +1311,26 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -1308,9 +1353,12 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1347,36 +1395,39 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-21200</v>
+        <v>9300</v>
       </c>
       <c r="E26" s="3">
-        <v>-84100</v>
+        <v>-21100</v>
       </c>
       <c r="F26" s="3">
-        <v>56100</v>
+        <v>-83600</v>
       </c>
       <c r="G26" s="3">
+        <v>55700</v>
+      </c>
+      <c r="H26" s="3">
         <v>5100</v>
       </c>
-      <c r="H26" s="3">
-        <v>-120800</v>
-      </c>
       <c r="I26" s="3">
-        <v>-85000</v>
+        <v>-120100</v>
       </c>
       <c r="J26" s="3">
+        <v>-84500</v>
+      </c>
+      <c r="K26" s="3">
         <v>-108500</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1386,36 +1437,39 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-10500</v>
+        <v>4900</v>
       </c>
       <c r="E27" s="3">
-        <v>-80900</v>
+        <v>-10400</v>
       </c>
       <c r="F27" s="3">
-        <v>67500</v>
+        <v>-80400</v>
       </c>
       <c r="G27" s="3">
+        <v>67100</v>
+      </c>
+      <c r="H27" s="3">
         <v>5500</v>
       </c>
-      <c r="H27" s="3">
-        <v>-122700</v>
-      </c>
       <c r="I27" s="3">
-        <v>-85200</v>
+        <v>-122000</v>
       </c>
       <c r="J27" s="3">
+        <v>-84700</v>
+      </c>
+      <c r="K27" s="3">
         <v>-148500</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1425,9 +1479,12 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1464,9 +1521,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1503,9 +1563,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1542,9 +1605,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1581,36 +1647,39 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6900</v>
+        <v>-32100</v>
       </c>
       <c r="E32" s="3">
-        <v>-6100</v>
+        <v>-6800</v>
       </c>
       <c r="F32" s="3">
-        <v>-16400</v>
+        <v>-6000</v>
       </c>
       <c r="G32" s="3">
-        <v>-23400</v>
+        <v>-16300</v>
       </c>
       <c r="H32" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="I32" s="3">
         <v>1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1620,36 +1689,39 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-10500</v>
+        <v>4900</v>
       </c>
       <c r="E33" s="3">
-        <v>-80900</v>
+        <v>-10400</v>
       </c>
       <c r="F33" s="3">
-        <v>67500</v>
+        <v>-80400</v>
       </c>
       <c r="G33" s="3">
+        <v>67100</v>
+      </c>
+      <c r="H33" s="3">
         <v>5500</v>
       </c>
-      <c r="H33" s="3">
-        <v>-122700</v>
-      </c>
       <c r="I33" s="3">
-        <v>-85200</v>
+        <v>-122000</v>
       </c>
       <c r="J33" s="3">
+        <v>-84700</v>
+      </c>
+      <c r="K33" s="3">
         <v>-148500</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1659,9 +1731,12 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1698,36 +1773,39 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-10500</v>
+        <v>4900</v>
       </c>
       <c r="E35" s="3">
-        <v>-80900</v>
+        <v>-10400</v>
       </c>
       <c r="F35" s="3">
-        <v>67500</v>
+        <v>-80400</v>
       </c>
       <c r="G35" s="3">
+        <v>67100</v>
+      </c>
+      <c r="H35" s="3">
         <v>5500</v>
       </c>
-      <c r="H35" s="3">
-        <v>-122700</v>
-      </c>
       <c r="I35" s="3">
-        <v>-85200</v>
+        <v>-122000</v>
       </c>
       <c r="J35" s="3">
+        <v>-84700</v>
+      </c>
+      <c r="K35" s="3">
         <v>-148500</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,41 +1815,44 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1781,9 +1862,12 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1799,8 +1883,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1816,35 +1901,36 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>561900</v>
+        <v>613400</v>
       </c>
       <c r="E41" s="3">
-        <v>619500</v>
+        <v>558400</v>
       </c>
       <c r="F41" s="3">
-        <v>734000</v>
+        <v>615700</v>
       </c>
       <c r="G41" s="3">
-        <v>1124900</v>
+        <v>729500</v>
       </c>
       <c r="H41" s="3">
-        <v>773300</v>
+        <v>1118000</v>
       </c>
       <c r="I41" s="3">
-        <v>75000</v>
+        <v>768500</v>
       </c>
       <c r="J41" s="3">
+        <v>74600</v>
+      </c>
+      <c r="K41" s="3">
         <v>71800</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1854,23 +1940,26 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>349100</v>
+        <v>237200</v>
       </c>
       <c r="E42" s="3">
-        <v>288700</v>
+        <v>346900</v>
       </c>
       <c r="F42" s="3">
-        <v>310000</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
+        <v>286900</v>
+      </c>
+      <c r="G42" s="3">
+        <v>308100</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
@@ -1884,8 +1973,8 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -1893,36 +1982,39 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>64700</v>
+        <v>60400</v>
       </c>
       <c r="E43" s="3">
-        <v>76300</v>
+        <v>64300</v>
       </c>
       <c r="F43" s="3">
-        <v>58400</v>
+        <v>75800</v>
       </c>
       <c r="G43" s="3">
-        <v>55200</v>
+        <v>58000</v>
       </c>
       <c r="H43" s="3">
-        <v>53200</v>
+        <v>54900</v>
       </c>
       <c r="I43" s="3">
-        <v>32300</v>
+        <v>52800</v>
       </c>
       <c r="J43" s="3">
+        <v>32100</v>
+      </c>
+      <c r="K43" s="3">
         <v>16300</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1932,9 +2024,12 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1971,36 +2066,39 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>8200</v>
+        <v>12600</v>
       </c>
       <c r="E45" s="3">
-        <v>20500</v>
+        <v>8100</v>
       </c>
       <c r="F45" s="3">
-        <v>14400</v>
+        <v>20400</v>
       </c>
       <c r="G45" s="3">
-        <v>15600</v>
+        <v>14300</v>
       </c>
       <c r="H45" s="3">
-        <v>24000</v>
+        <v>15500</v>
       </c>
       <c r="I45" s="3">
-        <v>12700</v>
+        <v>23800</v>
       </c>
       <c r="J45" s="3">
+        <v>12600</v>
+      </c>
+      <c r="K45" s="3">
         <v>5800</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2010,36 +2108,39 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>983900</v>
+        <v>923700</v>
       </c>
       <c r="E46" s="3">
-        <v>1005000</v>
+        <v>977800</v>
       </c>
       <c r="F46" s="3">
-        <v>1116900</v>
+        <v>998800</v>
       </c>
       <c r="G46" s="3">
-        <v>1195800</v>
+        <v>1109900</v>
       </c>
       <c r="H46" s="3">
-        <v>850400</v>
+        <v>1188400</v>
       </c>
       <c r="I46" s="3">
-        <v>120000</v>
+        <v>845100</v>
       </c>
       <c r="J46" s="3">
+        <v>119200</v>
+      </c>
+      <c r="K46" s="3">
         <v>94000</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2049,36 +2150,39 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>108700</v>
+        <v>147300</v>
       </c>
       <c r="E47" s="3">
-        <v>82200</v>
+        <v>108000</v>
       </c>
       <c r="F47" s="3">
-        <v>83500</v>
+        <v>81700</v>
       </c>
       <c r="G47" s="3">
-        <v>31400</v>
+        <v>83000</v>
       </c>
       <c r="H47" s="3">
-        <v>18700</v>
+        <v>31200</v>
       </c>
       <c r="I47" s="3">
-        <v>13400</v>
+        <v>18500</v>
       </c>
       <c r="J47" s="3">
+        <v>13300</v>
+      </c>
+      <c r="K47" s="3">
         <v>4100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2088,26 +2192,29 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>9300</v>
+        <v>5100</v>
       </c>
       <c r="E48" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F48" s="3">
         <v>13500</v>
       </c>
-      <c r="F48" s="3">
-        <v>13900</v>
-      </c>
       <c r="G48" s="3">
+        <v>13800</v>
+      </c>
+      <c r="H48" s="3">
         <v>5400</v>
-      </c>
-      <c r="H48" s="3">
-        <v>7000</v>
       </c>
       <c r="I48" s="3">
         <v>7000</v>
@@ -2115,8 +2222,8 @@
       <c r="J48" s="3">
         <v>6900</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
+      <c r="K48" s="3">
+        <v>6900</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
@@ -2127,36 +2234,39 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>16800</v>
+        <v>16700</v>
       </c>
       <c r="E49" s="3">
-        <v>24200</v>
+        <v>16700</v>
       </c>
       <c r="F49" s="3">
-        <v>21500</v>
+        <v>24100</v>
       </c>
       <c r="G49" s="3">
-        <v>31800</v>
+        <v>21400</v>
       </c>
       <c r="H49" s="3">
-        <v>20100</v>
+        <v>31600</v>
       </c>
       <c r="I49" s="3">
+        <v>20000</v>
+      </c>
+      <c r="J49" s="3">
         <v>2300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1600</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2166,9 +2276,12 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2205,9 +2318,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2244,36 +2360,39 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E52" s="3">
         <v>13700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3">
-        <v>6800</v>
-      </c>
       <c r="I52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J52" s="3">
         <v>800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1800</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2283,9 +2402,12 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2322,36 +2444,39 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1132400</v>
+        <v>1115200</v>
       </c>
       <c r="E54" s="3">
-        <v>1134000</v>
+        <v>1125400</v>
       </c>
       <c r="F54" s="3">
-        <v>1238400</v>
+        <v>1127000</v>
       </c>
       <c r="G54" s="3">
-        <v>1265600</v>
+        <v>1230700</v>
       </c>
       <c r="H54" s="3">
-        <v>902900</v>
+        <v>1257800</v>
       </c>
       <c r="I54" s="3">
-        <v>143400</v>
+        <v>897300</v>
       </c>
       <c r="J54" s="3">
+        <v>142500</v>
+      </c>
+      <c r="K54" s="3">
         <v>108300</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2361,9 +2486,12 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2379,8 +2507,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2396,35 +2525,36 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>92700</v>
+        <v>73800</v>
       </c>
       <c r="E57" s="3">
-        <v>114600</v>
+        <v>92200</v>
       </c>
       <c r="F57" s="3">
-        <v>137100</v>
+        <v>113900</v>
       </c>
       <c r="G57" s="3">
-        <v>123700</v>
+        <v>136200</v>
       </c>
       <c r="H57" s="3">
-        <v>111300</v>
+        <v>123000</v>
       </c>
       <c r="I57" s="3">
-        <v>62800</v>
+        <v>110600</v>
       </c>
       <c r="J57" s="3">
+        <v>62500</v>
+      </c>
+      <c r="K57" s="3">
         <v>46700</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,9 +2564,12 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2473,36 +2606,39 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>124000</v>
+        <v>116300</v>
       </c>
       <c r="E59" s="3">
-        <v>142500</v>
+        <v>123200</v>
       </c>
       <c r="F59" s="3">
-        <v>124700</v>
+        <v>141600</v>
       </c>
       <c r="G59" s="3">
-        <v>125700</v>
+        <v>123900</v>
       </c>
       <c r="H59" s="3">
-        <v>286900</v>
+        <v>124900</v>
       </c>
       <c r="I59" s="3">
-        <v>58400</v>
+        <v>285100</v>
       </c>
       <c r="J59" s="3">
+        <v>58000</v>
+      </c>
+      <c r="K59" s="3">
         <v>26100</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2512,36 +2648,39 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>216700</v>
+        <v>190100</v>
       </c>
       <c r="E60" s="3">
-        <v>257000</v>
+        <v>215300</v>
       </c>
       <c r="F60" s="3">
-        <v>261800</v>
+        <v>255500</v>
       </c>
       <c r="G60" s="3">
-        <v>249400</v>
+        <v>260100</v>
       </c>
       <c r="H60" s="3">
-        <v>398100</v>
+        <v>247900</v>
       </c>
       <c r="I60" s="3">
-        <v>121200</v>
+        <v>395700</v>
       </c>
       <c r="J60" s="3">
+        <v>120500</v>
+      </c>
+      <c r="K60" s="3">
         <v>72800</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2551,9 +2690,12 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2590,27 +2732,30 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>900</v>
+      </c>
+      <c r="E62" s="3">
         <v>3600</v>
       </c>
-      <c r="E62" s="3">
-        <v>6900</v>
-      </c>
       <c r="F62" s="3">
+        <v>6800</v>
+      </c>
+      <c r="G62" s="3">
         <v>6600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6400</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2626,12 +2771,15 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2668,9 +2816,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2707,9 +2858,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2746,36 +2900,39 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>220300</v>
+        <v>191000</v>
       </c>
       <c r="E66" s="3">
-        <v>263900</v>
+        <v>219000</v>
       </c>
       <c r="F66" s="3">
-        <v>273700</v>
+        <v>262300</v>
       </c>
       <c r="G66" s="3">
-        <v>258800</v>
+        <v>272000</v>
       </c>
       <c r="H66" s="3">
-        <v>398100</v>
+        <v>257200</v>
       </c>
       <c r="I66" s="3">
-        <v>121200</v>
+        <v>395700</v>
       </c>
       <c r="J66" s="3">
+        <v>120500</v>
+      </c>
+      <c r="K66" s="3">
         <v>72800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2785,9 +2942,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2803,8 +2963,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2841,9 +3002,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2880,9 +3044,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2899,17 +3066,17 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>923800</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>365500</v>
+        <v>918000</v>
       </c>
       <c r="J70" s="3">
+        <v>363300</v>
+      </c>
+      <c r="K70" s="3">
         <v>296000</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -2919,9 +3086,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2958,36 +3128,39 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-489400</v>
+        <v>-481500</v>
       </c>
       <c r="E72" s="3">
-        <v>-478900</v>
+        <v>-486400</v>
       </c>
       <c r="F72" s="3">
-        <v>-398000</v>
+        <v>-476000</v>
       </c>
       <c r="G72" s="3">
-        <v>-465500</v>
+        <v>-395600</v>
       </c>
       <c r="H72" s="3">
-        <v>-471100</v>
+        <v>-462700</v>
       </c>
       <c r="I72" s="3">
-        <v>-349200</v>
+        <v>-468200</v>
       </c>
       <c r="J72" s="3">
+        <v>-347100</v>
+      </c>
+      <c r="K72" s="3">
         <v>-264000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,9 +3170,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3036,9 +3212,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3075,9 +3254,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3114,36 +3296,39 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>912000</v>
+        <v>924200</v>
       </c>
       <c r="E76" s="3">
-        <v>870100</v>
+        <v>906400</v>
       </c>
       <c r="F76" s="3">
-        <v>964700</v>
+        <v>864700</v>
       </c>
       <c r="G76" s="3">
-        <v>1006800</v>
+        <v>958700</v>
       </c>
       <c r="H76" s="3">
-        <v>-419000</v>
+        <v>1000500</v>
       </c>
       <c r="I76" s="3">
-        <v>-343300</v>
+        <v>-416300</v>
       </c>
       <c r="J76" s="3">
+        <v>-341200</v>
+      </c>
+      <c r="K76" s="3">
         <v>-260500</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3153,9 +3338,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3192,41 +3380,44 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3236,36 +3427,39 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-10500</v>
+        <v>4900</v>
       </c>
       <c r="E81" s="3">
-        <v>-80900</v>
+        <v>-10400</v>
       </c>
       <c r="F81" s="3">
-        <v>67500</v>
+        <v>-80400</v>
       </c>
       <c r="G81" s="3">
+        <v>67100</v>
+      </c>
+      <c r="H81" s="3">
         <v>5500</v>
       </c>
-      <c r="H81" s="3">
-        <v>-122700</v>
-      </c>
       <c r="I81" s="3">
-        <v>-85200</v>
+        <v>-122000</v>
       </c>
       <c r="J81" s="3">
+        <v>-84700</v>
+      </c>
+      <c r="K81" s="3">
         <v>-148500</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,9 +3469,12 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3293,35 +3490,36 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12200</v>
+        <v>13400</v>
       </c>
       <c r="E83" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F83" s="3">
         <v>12300</v>
       </c>
-      <c r="F83" s="3">
-        <v>15400</v>
-      </c>
       <c r="G83" s="3">
+        <v>15300</v>
+      </c>
+      <c r="H83" s="3">
         <v>12500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3331,9 +3529,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3370,9 +3571,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3409,9 +3613,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3448,9 +3655,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3487,9 +3697,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3526,36 +3739,39 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9400</v>
       </c>
-      <c r="E89" s="3">
-        <v>-81500</v>
-      </c>
       <c r="F89" s="3">
-        <v>92800</v>
+        <v>-81000</v>
       </c>
       <c r="G89" s="3">
-        <v>113000</v>
+        <v>92200</v>
       </c>
       <c r="H89" s="3">
-        <v>-46900</v>
+        <v>112300</v>
       </c>
       <c r="I89" s="3">
-        <v>-53000</v>
+        <v>-46600</v>
       </c>
       <c r="J89" s="3">
+        <v>-52600</v>
+      </c>
+      <c r="K89" s="3">
         <v>-99300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3565,9 +3781,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3583,35 +3802,36 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
-        <v>-1000</v>
-      </c>
       <c r="F91" s="3">
-        <v>-2700</v>
+        <v>-900</v>
       </c>
       <c r="G91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="H91" s="3">
         <v>-2200</v>
       </c>
-      <c r="H91" s="3">
-        <v>-4600</v>
-      </c>
       <c r="I91" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="J91" s="3">
         <v>-3300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6200</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,9 +3841,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3660,9 +3883,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3699,36 +3925,39 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-84600</v>
+        <v>57200</v>
       </c>
       <c r="E94" s="3">
-        <v>-2700</v>
+        <v>-84100</v>
       </c>
       <c r="F94" s="3">
-        <v>-363200</v>
+        <v>-2600</v>
       </c>
       <c r="G94" s="3">
-        <v>-34200</v>
+        <v>-361000</v>
       </c>
       <c r="H94" s="3">
-        <v>-36800</v>
+        <v>-34000</v>
       </c>
       <c r="I94" s="3">
-        <v>-12800</v>
+        <v>-36600</v>
       </c>
       <c r="J94" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-12000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,9 +3967,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3756,8 +3988,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3794,9 +4027,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3833,9 +4069,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3872,9 +4111,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3911,36 +4153,39 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-15100</v>
       </c>
-      <c r="E100" s="3">
-        <v>-14900</v>
-      </c>
       <c r="F100" s="3">
-        <v>-66600</v>
+        <v>-14800</v>
       </c>
       <c r="G100" s="3">
-        <v>263600</v>
+        <v>-66200</v>
       </c>
       <c r="H100" s="3">
-        <v>734000</v>
+        <v>262000</v>
       </c>
       <c r="I100" s="3">
-        <v>69500</v>
+        <v>729500</v>
       </c>
       <c r="J100" s="3">
+        <v>69100</v>
+      </c>
+      <c r="K100" s="3">
         <v>180500</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3950,36 +4195,39 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>50900</v>
+        <v>13100</v>
       </c>
       <c r="E101" s="3">
-        <v>-15600</v>
+        <v>50600</v>
       </c>
       <c r="F101" s="3">
-        <v>-58200</v>
+        <v>-15500</v>
       </c>
       <c r="G101" s="3">
-        <v>15200</v>
+        <v>-57900</v>
       </c>
       <c r="H101" s="3">
-        <v>48000</v>
+        <v>15100</v>
       </c>
       <c r="I101" s="3">
+        <v>47700</v>
+      </c>
+      <c r="J101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3989,36 +4237,39 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-58300</v>
+        <v>63700</v>
       </c>
       <c r="E102" s="3">
-        <v>-114600</v>
+        <v>-58000</v>
       </c>
       <c r="F102" s="3">
-        <v>-395200</v>
+        <v>-113900</v>
       </c>
       <c r="G102" s="3">
-        <v>357700</v>
+        <v>-392800</v>
       </c>
       <c r="H102" s="3">
-        <v>698200</v>
+        <v>355400</v>
       </c>
       <c r="I102" s="3">
-        <v>3200</v>
+        <v>693900</v>
       </c>
       <c r="J102" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K102" s="3">
         <v>69400</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4028,7 +4279,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/DOYU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOYU_YR_FIN.xlsx
@@ -724,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>764100</v>
+        <v>779700</v>
       </c>
       <c r="E8" s="3">
-        <v>982100</v>
+        <v>1002100</v>
       </c>
       <c r="F8" s="3">
-        <v>1266300</v>
+        <v>1292100</v>
       </c>
       <c r="G8" s="3">
-        <v>1326600</v>
+        <v>1353700</v>
       </c>
       <c r="H8" s="3">
-        <v>1006300</v>
+        <v>1026800</v>
       </c>
       <c r="I8" s="3">
-        <v>504900</v>
+        <v>515200</v>
       </c>
       <c r="J8" s="3">
-        <v>260500</v>
+        <v>265800</v>
       </c>
       <c r="K8" s="3">
         <v>109400</v>
@@ -766,25 +766,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>669600</v>
+        <v>683200</v>
       </c>
       <c r="E9" s="3">
-        <v>845300</v>
+        <v>862500</v>
       </c>
       <c r="F9" s="3">
-        <v>1115700</v>
+        <v>1138500</v>
       </c>
       <c r="G9" s="3">
-        <v>1111000</v>
+        <v>1133700</v>
       </c>
       <c r="H9" s="3">
-        <v>841000</v>
+        <v>858200</v>
       </c>
       <c r="I9" s="3">
-        <v>484000</v>
+        <v>493900</v>
       </c>
       <c r="J9" s="3">
-        <v>261200</v>
+        <v>266500</v>
       </c>
       <c r="K9" s="3">
         <v>160600</v>
@@ -808,25 +808,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>94500</v>
+        <v>96400</v>
       </c>
       <c r="E10" s="3">
-        <v>136800</v>
+        <v>139600</v>
       </c>
       <c r="F10" s="3">
-        <v>150600</v>
+        <v>153700</v>
       </c>
       <c r="G10" s="3">
-        <v>215600</v>
+        <v>220000</v>
       </c>
       <c r="H10" s="3">
-        <v>165300</v>
+        <v>168600</v>
       </c>
       <c r="I10" s="3">
-        <v>20900</v>
+        <v>21300</v>
       </c>
       <c r="J10" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="K10" s="3">
         <v>-51200</v>
@@ -868,25 +868,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>38300</v>
+        <v>39000</v>
       </c>
       <c r="E12" s="3">
-        <v>52900</v>
+        <v>54000</v>
       </c>
       <c r="F12" s="3">
-        <v>67700</v>
+        <v>69100</v>
       </c>
       <c r="G12" s="3">
-        <v>57500</v>
+        <v>58700</v>
       </c>
       <c r="H12" s="3">
-        <v>53000</v>
+        <v>54100</v>
       </c>
       <c r="I12" s="3">
-        <v>45500</v>
+        <v>46400</v>
       </c>
       <c r="J12" s="3">
-        <v>29300</v>
+        <v>29900</v>
       </c>
       <c r="K12" s="3">
         <v>13000</v>
@@ -952,7 +952,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>3</v>
       </c>
       <c r="I14" s="3">
-        <v>-3200</v>
+        <v>-3300</v>
       </c>
       <c r="J14" s="3">
         <v>-900</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>786700</v>
+        <v>802800</v>
       </c>
       <c r="E17" s="3">
-        <v>1009600</v>
+        <v>1030200</v>
       </c>
       <c r="F17" s="3">
-        <v>1355900</v>
+        <v>1383600</v>
       </c>
       <c r="G17" s="3">
-        <v>1287100</v>
+        <v>1313400</v>
       </c>
       <c r="H17" s="3">
-        <v>1024400</v>
+        <v>1045400</v>
       </c>
       <c r="I17" s="3">
-        <v>623600</v>
+        <v>636300</v>
       </c>
       <c r="J17" s="3">
-        <v>346000</v>
+        <v>353000</v>
       </c>
       <c r="K17" s="3">
         <v>217300</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-22700</v>
+        <v>-23100</v>
       </c>
       <c r="E18" s="3">
-        <v>-27500</v>
+        <v>-28000</v>
       </c>
       <c r="F18" s="3">
-        <v>-89600</v>
+        <v>-91400</v>
       </c>
       <c r="G18" s="3">
-        <v>39500</v>
+        <v>40300</v>
       </c>
       <c r="H18" s="3">
-        <v>-18200</v>
+        <v>-18600</v>
       </c>
       <c r="I18" s="3">
-        <v>-118700</v>
+        <v>-121100</v>
       </c>
       <c r="J18" s="3">
-        <v>-85400</v>
+        <v>-87200</v>
       </c>
       <c r="K18" s="3">
         <v>-107900</v>
@@ -1153,19 +1153,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>32100</v>
+        <v>32700</v>
       </c>
       <c r="E20" s="3">
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="F20" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="G20" s="3">
-        <v>16300</v>
+        <v>16600</v>
       </c>
       <c r="H20" s="3">
-        <v>23200</v>
+        <v>23700</v>
       </c>
       <c r="I20" s="3">
         <v>-1400</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>22800</v>
+        <v>23200</v>
       </c>
       <c r="E21" s="3">
-        <v>-8600</v>
+        <v>-8800</v>
       </c>
       <c r="F21" s="3">
-        <v>-71400</v>
+        <v>-72800</v>
       </c>
       <c r="G21" s="3">
-        <v>71000</v>
+        <v>72500</v>
       </c>
       <c r="H21" s="3">
-        <v>17500</v>
+        <v>17800</v>
       </c>
       <c r="I21" s="3">
-        <v>-113800</v>
+        <v>-116100</v>
       </c>
       <c r="J21" s="3">
-        <v>-80900</v>
+        <v>-82600</v>
       </c>
       <c r="K21" s="3">
         <v>-106300</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>9400</v>
+        <v>9600</v>
       </c>
       <c r="E23" s="3">
-        <v>-20600</v>
+        <v>-21100</v>
       </c>
       <c r="F23" s="3">
-        <v>-83600</v>
+        <v>-85300</v>
       </c>
       <c r="G23" s="3">
-        <v>55700</v>
+        <v>56900</v>
       </c>
       <c r="H23" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="I23" s="3">
-        <v>-120100</v>
+        <v>-122500</v>
       </c>
       <c r="J23" s="3">
-        <v>-84500</v>
+        <v>-86200</v>
       </c>
       <c r="K23" s="3">
         <v>-108500</v>
@@ -1321,7 +1321,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
         <v>500</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>9300</v>
+        <v>9500</v>
       </c>
       <c r="E26" s="3">
-        <v>-21100</v>
+        <v>-21500</v>
       </c>
       <c r="F26" s="3">
-        <v>-83600</v>
+        <v>-85300</v>
       </c>
       <c r="G26" s="3">
-        <v>55700</v>
+        <v>56900</v>
       </c>
       <c r="H26" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="I26" s="3">
-        <v>-120100</v>
+        <v>-122500</v>
       </c>
       <c r="J26" s="3">
-        <v>-84500</v>
+        <v>-86200</v>
       </c>
       <c r="K26" s="3">
         <v>-108500</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="E27" s="3">
-        <v>-10400</v>
+        <v>-10600</v>
       </c>
       <c r="F27" s="3">
-        <v>-80400</v>
+        <v>-82000</v>
       </c>
       <c r="G27" s="3">
-        <v>67100</v>
+        <v>68400</v>
       </c>
       <c r="H27" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="I27" s="3">
-        <v>-122000</v>
+        <v>-124500</v>
       </c>
       <c r="J27" s="3">
-        <v>-84700</v>
+        <v>-86400</v>
       </c>
       <c r="K27" s="3">
         <v>-148500</v>
@@ -1657,19 +1657,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-32100</v>
+        <v>-32700</v>
       </c>
       <c r="E32" s="3">
-        <v>-6800</v>
+        <v>-7000</v>
       </c>
       <c r="F32" s="3">
-        <v>-6000</v>
+        <v>-6100</v>
       </c>
       <c r="G32" s="3">
-        <v>-16300</v>
+        <v>-16600</v>
       </c>
       <c r="H32" s="3">
-        <v>-23200</v>
+        <v>-23700</v>
       </c>
       <c r="I32" s="3">
         <v>1400</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="E33" s="3">
-        <v>-10400</v>
+        <v>-10600</v>
       </c>
       <c r="F33" s="3">
-        <v>-80400</v>
+        <v>-82000</v>
       </c>
       <c r="G33" s="3">
-        <v>67100</v>
+        <v>68400</v>
       </c>
       <c r="H33" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="I33" s="3">
-        <v>-122000</v>
+        <v>-124500</v>
       </c>
       <c r="J33" s="3">
-        <v>-84700</v>
+        <v>-86400</v>
       </c>
       <c r="K33" s="3">
         <v>-148500</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="E35" s="3">
-        <v>-10400</v>
+        <v>-10600</v>
       </c>
       <c r="F35" s="3">
-        <v>-80400</v>
+        <v>-82000</v>
       </c>
       <c r="G35" s="3">
-        <v>67100</v>
+        <v>68400</v>
       </c>
       <c r="H35" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="I35" s="3">
-        <v>-122000</v>
+        <v>-124500</v>
       </c>
       <c r="J35" s="3">
-        <v>-84700</v>
+        <v>-86400</v>
       </c>
       <c r="K35" s="3">
         <v>-148500</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>613400</v>
+        <v>626000</v>
       </c>
       <c r="E41" s="3">
-        <v>558400</v>
+        <v>569800</v>
       </c>
       <c r="F41" s="3">
-        <v>615700</v>
+        <v>628300</v>
       </c>
       <c r="G41" s="3">
-        <v>729500</v>
+        <v>744400</v>
       </c>
       <c r="H41" s="3">
-        <v>1118000</v>
+        <v>1140800</v>
       </c>
       <c r="I41" s="3">
-        <v>768500</v>
+        <v>784200</v>
       </c>
       <c r="J41" s="3">
-        <v>74600</v>
+        <v>76100</v>
       </c>
       <c r="K41" s="3">
         <v>71800</v>
@@ -1950,16 +1950,16 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>237200</v>
+        <v>242000</v>
       </c>
       <c r="E42" s="3">
-        <v>346900</v>
+        <v>354000</v>
       </c>
       <c r="F42" s="3">
-        <v>286900</v>
+        <v>292700</v>
       </c>
       <c r="G42" s="3">
-        <v>308100</v>
+        <v>314400</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>60400</v>
+        <v>61700</v>
       </c>
       <c r="E43" s="3">
-        <v>64300</v>
+        <v>65600</v>
       </c>
       <c r="F43" s="3">
-        <v>75800</v>
+        <v>77400</v>
       </c>
       <c r="G43" s="3">
-        <v>58000</v>
+        <v>59200</v>
       </c>
       <c r="H43" s="3">
-        <v>54900</v>
+        <v>56000</v>
       </c>
       <c r="I43" s="3">
-        <v>52800</v>
+        <v>53900</v>
       </c>
       <c r="J43" s="3">
-        <v>32100</v>
+        <v>32700</v>
       </c>
       <c r="K43" s="3">
         <v>16300</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>12600</v>
+        <v>12900</v>
       </c>
       <c r="E45" s="3">
-        <v>8100</v>
+        <v>8300</v>
       </c>
       <c r="F45" s="3">
-        <v>20400</v>
+        <v>20800</v>
       </c>
       <c r="G45" s="3">
-        <v>14300</v>
+        <v>14600</v>
       </c>
       <c r="H45" s="3">
-        <v>15500</v>
+        <v>15900</v>
       </c>
       <c r="I45" s="3">
-        <v>23800</v>
+        <v>24300</v>
       </c>
       <c r="J45" s="3">
-        <v>12600</v>
+        <v>12800</v>
       </c>
       <c r="K45" s="3">
         <v>5800</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>923700</v>
+        <v>942500</v>
       </c>
       <c r="E46" s="3">
-        <v>977800</v>
+        <v>997700</v>
       </c>
       <c r="F46" s="3">
-        <v>998800</v>
+        <v>1019200</v>
       </c>
       <c r="G46" s="3">
-        <v>1109900</v>
+        <v>1132600</v>
       </c>
       <c r="H46" s="3">
-        <v>1188400</v>
+        <v>1212700</v>
       </c>
       <c r="I46" s="3">
-        <v>845100</v>
+        <v>862400</v>
       </c>
       <c r="J46" s="3">
-        <v>119200</v>
+        <v>121600</v>
       </c>
       <c r="K46" s="3">
         <v>94000</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>147300</v>
+        <v>150300</v>
       </c>
       <c r="E47" s="3">
-        <v>108000</v>
+        <v>110200</v>
       </c>
       <c r="F47" s="3">
-        <v>81700</v>
+        <v>83400</v>
       </c>
       <c r="G47" s="3">
-        <v>83000</v>
+        <v>84700</v>
       </c>
       <c r="H47" s="3">
-        <v>31200</v>
+        <v>31800</v>
       </c>
       <c r="I47" s="3">
-        <v>18500</v>
+        <v>18900</v>
       </c>
       <c r="J47" s="3">
-        <v>13300</v>
+        <v>13600</v>
       </c>
       <c r="K47" s="3">
         <v>4100</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="E48" s="3">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F48" s="3">
-        <v>13500</v>
+        <v>13700</v>
       </c>
       <c r="G48" s="3">
-        <v>13800</v>
+        <v>14100</v>
       </c>
       <c r="H48" s="3">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="I48" s="3">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="J48" s="3">
-        <v>6900</v>
+        <v>7100</v>
       </c>
       <c r="K48" s="3">
         <v>6900</v>
@@ -2244,22 +2244,22 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>16700</v>
+        <v>17000</v>
       </c>
       <c r="E49" s="3">
-        <v>16700</v>
+        <v>17000</v>
       </c>
       <c r="F49" s="3">
-        <v>24100</v>
+        <v>24600</v>
       </c>
       <c r="G49" s="3">
-        <v>21400</v>
+        <v>21800</v>
       </c>
       <c r="H49" s="3">
-        <v>31600</v>
+        <v>32300</v>
       </c>
       <c r="I49" s="3">
-        <v>20000</v>
+        <v>20400</v>
       </c>
       <c r="J49" s="3">
         <v>2300</v>
@@ -2370,22 +2370,22 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>22500</v>
+        <v>23000</v>
       </c>
       <c r="E52" s="3">
-        <v>13700</v>
+        <v>13900</v>
       </c>
       <c r="F52" s="3">
-        <v>9000</v>
+        <v>9100</v>
       </c>
       <c r="G52" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="H52" s="3">
         <v>1200</v>
       </c>
       <c r="I52" s="3">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="J52" s="3">
         <v>800</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1115200</v>
+        <v>1138000</v>
       </c>
       <c r="E54" s="3">
-        <v>1125400</v>
+        <v>1148300</v>
       </c>
       <c r="F54" s="3">
-        <v>1127000</v>
+        <v>1150000</v>
       </c>
       <c r="G54" s="3">
-        <v>1230700</v>
+        <v>1255800</v>
       </c>
       <c r="H54" s="3">
-        <v>1257800</v>
+        <v>1283400</v>
       </c>
       <c r="I54" s="3">
-        <v>897300</v>
+        <v>915600</v>
       </c>
       <c r="J54" s="3">
-        <v>142500</v>
+        <v>145400</v>
       </c>
       <c r="K54" s="3">
         <v>108300</v>
@@ -2532,25 +2532,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>73800</v>
+        <v>75300</v>
       </c>
       <c r="E57" s="3">
-        <v>92200</v>
+        <v>94000</v>
       </c>
       <c r="F57" s="3">
-        <v>113900</v>
+        <v>116200</v>
       </c>
       <c r="G57" s="3">
-        <v>136200</v>
+        <v>139000</v>
       </c>
       <c r="H57" s="3">
-        <v>123000</v>
+        <v>125500</v>
       </c>
       <c r="I57" s="3">
-        <v>110600</v>
+        <v>112800</v>
       </c>
       <c r="J57" s="3">
-        <v>62500</v>
+        <v>63700</v>
       </c>
       <c r="K57" s="3">
         <v>46700</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>116300</v>
+        <v>118700</v>
       </c>
       <c r="E59" s="3">
-        <v>123200</v>
+        <v>125700</v>
       </c>
       <c r="F59" s="3">
-        <v>141600</v>
+        <v>144500</v>
       </c>
       <c r="G59" s="3">
-        <v>123900</v>
+        <v>126400</v>
       </c>
       <c r="H59" s="3">
-        <v>124900</v>
+        <v>127500</v>
       </c>
       <c r="I59" s="3">
-        <v>285100</v>
+        <v>290900</v>
       </c>
       <c r="J59" s="3">
-        <v>58000</v>
+        <v>59200</v>
       </c>
       <c r="K59" s="3">
         <v>26100</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>190100</v>
+        <v>194000</v>
       </c>
       <c r="E60" s="3">
-        <v>215300</v>
+        <v>219700</v>
       </c>
       <c r="F60" s="3">
-        <v>255500</v>
+        <v>260700</v>
       </c>
       <c r="G60" s="3">
-        <v>260100</v>
+        <v>265400</v>
       </c>
       <c r="H60" s="3">
-        <v>247900</v>
+        <v>253000</v>
       </c>
       <c r="I60" s="3">
-        <v>395700</v>
+        <v>403800</v>
       </c>
       <c r="J60" s="3">
-        <v>120500</v>
+        <v>122900</v>
       </c>
       <c r="K60" s="3">
         <v>72800</v>
@@ -2745,16 +2745,16 @@
         <v>900</v>
       </c>
       <c r="E62" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="F62" s="3">
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="G62" s="3">
-        <v>6600</v>
+        <v>6700</v>
       </c>
       <c r="H62" s="3">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>191000</v>
+        <v>194900</v>
       </c>
       <c r="E66" s="3">
-        <v>219000</v>
+        <v>223400</v>
       </c>
       <c r="F66" s="3">
-        <v>262300</v>
+        <v>267600</v>
       </c>
       <c r="G66" s="3">
-        <v>272000</v>
+        <v>277600</v>
       </c>
       <c r="H66" s="3">
-        <v>257200</v>
+        <v>262500</v>
       </c>
       <c r="I66" s="3">
-        <v>395700</v>
+        <v>403800</v>
       </c>
       <c r="J66" s="3">
-        <v>120500</v>
+        <v>122900</v>
       </c>
       <c r="K66" s="3">
         <v>72800</v>
@@ -3069,10 +3069,10 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>918000</v>
+        <v>936800</v>
       </c>
       <c r="J70" s="3">
-        <v>363300</v>
+        <v>370700</v>
       </c>
       <c r="K70" s="3">
         <v>296000</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-481500</v>
+        <v>-491300</v>
       </c>
       <c r="E72" s="3">
-        <v>-486400</v>
+        <v>-496300</v>
       </c>
       <c r="F72" s="3">
-        <v>-476000</v>
+        <v>-485700</v>
       </c>
       <c r="G72" s="3">
-        <v>-395600</v>
+        <v>-403700</v>
       </c>
       <c r="H72" s="3">
-        <v>-462700</v>
+        <v>-472100</v>
       </c>
       <c r="I72" s="3">
-        <v>-468200</v>
+        <v>-477700</v>
       </c>
       <c r="J72" s="3">
-        <v>-347100</v>
+        <v>-354200</v>
       </c>
       <c r="K72" s="3">
         <v>-264000</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>924200</v>
+        <v>943100</v>
       </c>
       <c r="E76" s="3">
-        <v>906400</v>
+        <v>924900</v>
       </c>
       <c r="F76" s="3">
-        <v>864700</v>
+        <v>882300</v>
       </c>
       <c r="G76" s="3">
-        <v>958700</v>
+        <v>978300</v>
       </c>
       <c r="H76" s="3">
-        <v>1000500</v>
+        <v>1021000</v>
       </c>
       <c r="I76" s="3">
-        <v>-416300</v>
+        <v>-424900</v>
       </c>
       <c r="J76" s="3">
-        <v>-341200</v>
+        <v>-348200</v>
       </c>
       <c r="K76" s="3">
         <v>-260500</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="E81" s="3">
-        <v>-10400</v>
+        <v>-10600</v>
       </c>
       <c r="F81" s="3">
-        <v>-80400</v>
+        <v>-82000</v>
       </c>
       <c r="G81" s="3">
-        <v>67100</v>
+        <v>68400</v>
       </c>
       <c r="H81" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="I81" s="3">
-        <v>-122000</v>
+        <v>-124500</v>
       </c>
       <c r="J81" s="3">
-        <v>-84700</v>
+        <v>-86400</v>
       </c>
       <c r="K81" s="3">
         <v>-148500</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>13400</v>
+        <v>13700</v>
       </c>
       <c r="E83" s="3">
-        <v>12100</v>
+        <v>12300</v>
       </c>
       <c r="F83" s="3">
-        <v>12300</v>
+        <v>12500</v>
       </c>
       <c r="G83" s="3">
-        <v>15300</v>
+        <v>15600</v>
       </c>
       <c r="H83" s="3">
-        <v>12500</v>
+        <v>12700</v>
       </c>
       <c r="I83" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="J83" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="K83" s="3">
         <v>1000</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-6600</v>
+        <v>-6700</v>
       </c>
       <c r="E89" s="3">
-        <v>-9400</v>
+        <v>-9600</v>
       </c>
       <c r="F89" s="3">
-        <v>-81000</v>
+        <v>-82700</v>
       </c>
       <c r="G89" s="3">
-        <v>92200</v>
+        <v>94100</v>
       </c>
       <c r="H89" s="3">
-        <v>112300</v>
+        <v>114600</v>
       </c>
       <c r="I89" s="3">
-        <v>-46600</v>
+        <v>-47600</v>
       </c>
       <c r="J89" s="3">
-        <v>-52600</v>
+        <v>-53700</v>
       </c>
       <c r="K89" s="3">
         <v>-99300</v>
@@ -3815,19 +3815,19 @@
         <v>-800</v>
       </c>
       <c r="F91" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="G91" s="3">
-        <v>-2600</v>
+        <v>-2700</v>
       </c>
       <c r="H91" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="I91" s="3">
-        <v>-4500</v>
+        <v>-4600</v>
       </c>
       <c r="J91" s="3">
-        <v>-3300</v>
+        <v>-3400</v>
       </c>
       <c r="K91" s="3">
         <v>-6200</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>57200</v>
+        <v>58400</v>
       </c>
       <c r="E94" s="3">
-        <v>-84100</v>
+        <v>-85800</v>
       </c>
       <c r="F94" s="3">
-        <v>-2600</v>
+        <v>-2700</v>
       </c>
       <c r="G94" s="3">
-        <v>-361000</v>
+        <v>-368300</v>
       </c>
       <c r="H94" s="3">
-        <v>-34000</v>
+        <v>-34700</v>
       </c>
       <c r="I94" s="3">
-        <v>-36600</v>
+        <v>-37400</v>
       </c>
       <c r="J94" s="3">
-        <v>-12700</v>
+        <v>-13000</v>
       </c>
       <c r="K94" s="3">
         <v>-12000</v>
@@ -4166,22 +4166,22 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-15100</v>
       </c>
-      <c r="F100" s="3">
-        <v>-14800</v>
-      </c>
       <c r="G100" s="3">
-        <v>-66200</v>
+        <v>-67600</v>
       </c>
       <c r="H100" s="3">
-        <v>262000</v>
+        <v>267300</v>
       </c>
       <c r="I100" s="3">
-        <v>729500</v>
+        <v>744400</v>
       </c>
       <c r="J100" s="3">
-        <v>69100</v>
+        <v>70500</v>
       </c>
       <c r="K100" s="3">
         <v>180500</v>
@@ -4205,22 +4205,22 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>13100</v>
+        <v>13400</v>
       </c>
       <c r="E101" s="3">
-        <v>50600</v>
+        <v>51600</v>
       </c>
       <c r="F101" s="3">
-        <v>-15500</v>
+        <v>-15800</v>
       </c>
       <c r="G101" s="3">
-        <v>-57900</v>
+        <v>-59100</v>
       </c>
       <c r="H101" s="3">
-        <v>15100</v>
+        <v>15400</v>
       </c>
       <c r="I101" s="3">
-        <v>47700</v>
+        <v>48600</v>
       </c>
       <c r="J101" s="3">
         <v>-600</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>63700</v>
+        <v>65000</v>
       </c>
       <c r="E102" s="3">
-        <v>-58000</v>
+        <v>-59100</v>
       </c>
       <c r="F102" s="3">
-        <v>-113900</v>
+        <v>-116300</v>
       </c>
       <c r="G102" s="3">
-        <v>-392800</v>
+        <v>-400800</v>
       </c>
       <c r="H102" s="3">
-        <v>355400</v>
+        <v>362700</v>
       </c>
       <c r="I102" s="3">
-        <v>693900</v>
+        <v>708100</v>
       </c>
       <c r="J102" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="K102" s="3">
         <v>69400</v>

--- a/AAII_Financials/Yearly/DOYU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOYU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
   <si>
     <t>DOYU</t>
   </si>
@@ -724,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>779700</v>
+        <v>779900</v>
       </c>
       <c r="E8" s="3">
-        <v>1002100</v>
+        <v>1030600</v>
       </c>
       <c r="F8" s="3">
-        <v>1292100</v>
+        <v>1442800</v>
       </c>
       <c r="G8" s="3">
-        <v>1353700</v>
+        <v>1470700</v>
       </c>
       <c r="H8" s="3">
-        <v>1026800</v>
+        <v>1046000</v>
       </c>
       <c r="I8" s="3">
-        <v>515200</v>
+        <v>531300</v>
       </c>
       <c r="J8" s="3">
-        <v>265800</v>
+        <v>289800</v>
       </c>
       <c r="K8" s="3">
         <v>109400</v>
@@ -766,25 +766,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>683200</v>
+        <v>683500</v>
       </c>
       <c r="E9" s="3">
-        <v>862500</v>
+        <v>887000</v>
       </c>
       <c r="F9" s="3">
-        <v>1138500</v>
+        <v>1271200</v>
       </c>
       <c r="G9" s="3">
-        <v>1133700</v>
+        <v>1231700</v>
       </c>
       <c r="H9" s="3">
-        <v>858200</v>
+        <v>874200</v>
       </c>
       <c r="I9" s="3">
-        <v>493900</v>
+        <v>509400</v>
       </c>
       <c r="J9" s="3">
-        <v>266500</v>
+        <v>290500</v>
       </c>
       <c r="K9" s="3">
         <v>160600</v>
@@ -808,22 +808,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>96400</v>
+        <v>96500</v>
       </c>
       <c r="E10" s="3">
-        <v>139600</v>
+        <v>143600</v>
       </c>
       <c r="F10" s="3">
-        <v>153700</v>
+        <v>171600</v>
       </c>
       <c r="G10" s="3">
-        <v>220000</v>
+        <v>239000</v>
       </c>
       <c r="H10" s="3">
-        <v>168600</v>
+        <v>171800</v>
       </c>
       <c r="I10" s="3">
-        <v>21300</v>
+        <v>22000</v>
       </c>
       <c r="J10" s="3">
         <v>-700</v>
@@ -868,25 +868,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>39000</v>
+        <v>35500</v>
       </c>
       <c r="E12" s="3">
-        <v>54000</v>
+        <v>49600</v>
       </c>
       <c r="F12" s="3">
-        <v>69100</v>
+        <v>69500</v>
       </c>
       <c r="G12" s="3">
-        <v>58700</v>
+        <v>55800</v>
       </c>
       <c r="H12" s="3">
-        <v>54100</v>
+        <v>55100</v>
       </c>
       <c r="I12" s="3">
-        <v>46400</v>
+        <v>47900</v>
       </c>
       <c r="J12" s="3">
-        <v>29900</v>
+        <v>32600</v>
       </c>
       <c r="K12" s="3">
         <v>13000</v>
@@ -952,25 +952,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2000</v>
+        <v>9700</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>11900</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="G14" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+        <v>600</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2700</v>
       </c>
       <c r="I14" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="J14" s="3">
-        <v>-900</v>
+        <v>2700</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -994,25 +994,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>13700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>12700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>12900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>802800</v>
+        <v>800800</v>
       </c>
       <c r="E17" s="3">
-        <v>1030200</v>
+        <v>1059200</v>
       </c>
       <c r="F17" s="3">
-        <v>1383600</v>
+        <v>1544900</v>
       </c>
       <c r="G17" s="3">
-        <v>1313400</v>
+        <v>1430600</v>
       </c>
       <c r="H17" s="3">
-        <v>1045400</v>
+        <v>1064900</v>
       </c>
       <c r="I17" s="3">
-        <v>636300</v>
+        <v>656200</v>
       </c>
       <c r="J17" s="3">
-        <v>353000</v>
+        <v>384900</v>
       </c>
       <c r="K17" s="3">
         <v>217300</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-23100</v>
+        <v>-20900</v>
       </c>
       <c r="E18" s="3">
-        <v>-28000</v>
+        <v>-28600</v>
       </c>
       <c r="F18" s="3">
-        <v>-91400</v>
+        <v>-102100</v>
       </c>
       <c r="G18" s="3">
-        <v>40300</v>
+        <v>40100</v>
       </c>
       <c r="H18" s="3">
-        <v>-18600</v>
+        <v>-18900</v>
       </c>
       <c r="I18" s="3">
-        <v>-121100</v>
+        <v>-124900</v>
       </c>
       <c r="J18" s="3">
-        <v>-87200</v>
+        <v>-95000</v>
       </c>
       <c r="K18" s="3">
         <v>-107900</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>32700</v>
+        <v>4400</v>
       </c>
       <c r="E20" s="3">
-        <v>7000</v>
+        <v>-9000</v>
       </c>
       <c r="F20" s="3">
-        <v>6100</v>
+        <v>2400</v>
       </c>
       <c r="G20" s="3">
-        <v>16600</v>
+        <v>-200</v>
       </c>
       <c r="H20" s="3">
-        <v>23700</v>
+        <v>-3600</v>
       </c>
       <c r="I20" s="3">
-        <v>-1400</v>
+        <v>12300</v>
       </c>
       <c r="J20" s="3">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>600</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>23200</v>
+        <v>-11600</v>
       </c>
       <c r="E21" s="3">
-        <v>-8800</v>
+        <v>-6900</v>
       </c>
       <c r="F21" s="3">
-        <v>-72800</v>
+        <v>-90500</v>
       </c>
       <c r="G21" s="3">
-        <v>72500</v>
+        <v>57300</v>
       </c>
       <c r="H21" s="3">
-        <v>17800</v>
+        <v>-2400</v>
       </c>
       <c r="I21" s="3">
-        <v>-116100</v>
+        <v>-130500</v>
       </c>
       <c r="J21" s="3">
-        <v>-82600</v>
+        <v>-91200</v>
       </c>
       <c r="K21" s="3">
         <v>-106300</v>
@@ -1251,11 +1251,11 @@
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>1200</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>9600</v>
+        <v>5200</v>
       </c>
       <c r="E23" s="3">
-        <v>-21100</v>
+        <v>-12600</v>
       </c>
       <c r="F23" s="3">
-        <v>-85300</v>
+        <v>-97600</v>
       </c>
       <c r="G23" s="3">
-        <v>56900</v>
+        <v>62000</v>
       </c>
       <c r="H23" s="3">
-        <v>5200</v>
+        <v>4800</v>
       </c>
       <c r="I23" s="3">
-        <v>-122500</v>
+        <v>-127400</v>
       </c>
       <c r="J23" s="3">
-        <v>-86200</v>
+        <v>-94200</v>
       </c>
       <c r="K23" s="3">
         <v>-108500</v>
@@ -1332,14 +1332,14 @@
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>9500</v>
+        <v>5000</v>
       </c>
       <c r="E26" s="3">
-        <v>-21500</v>
+        <v>-13100</v>
       </c>
       <c r="F26" s="3">
-        <v>-85300</v>
+        <v>-97600</v>
       </c>
       <c r="G26" s="3">
-        <v>56900</v>
+        <v>62000</v>
       </c>
       <c r="H26" s="3">
-        <v>5200</v>
+        <v>4800</v>
       </c>
       <c r="I26" s="3">
-        <v>-122500</v>
+        <v>-127400</v>
       </c>
       <c r="J26" s="3">
-        <v>-86200</v>
+        <v>-94200</v>
       </c>
       <c r="K26" s="3">
         <v>-108500</v>
@@ -1450,22 +1450,22 @@
         <v>5000</v>
       </c>
       <c r="E27" s="3">
-        <v>-10600</v>
+        <v>-10900</v>
       </c>
       <c r="F27" s="3">
-        <v>-82000</v>
+        <v>-91600</v>
       </c>
       <c r="G27" s="3">
-        <v>68400</v>
+        <v>74400</v>
       </c>
       <c r="H27" s="3">
-        <v>5600</v>
+        <v>3700</v>
       </c>
       <c r="I27" s="3">
-        <v>-124500</v>
+        <v>-128400</v>
       </c>
       <c r="J27" s="3">
-        <v>-86400</v>
+        <v>-94200</v>
       </c>
       <c r="K27" s="3">
         <v>-148500</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-32700</v>
+        <v>-4400</v>
       </c>
       <c r="E32" s="3">
-        <v>-7000</v>
+        <v>9000</v>
       </c>
       <c r="F32" s="3">
-        <v>-6100</v>
+        <v>-2400</v>
       </c>
       <c r="G32" s="3">
-        <v>-16600</v>
+        <v>200</v>
       </c>
       <c r="H32" s="3">
-        <v>-23700</v>
+        <v>3600</v>
       </c>
       <c r="I32" s="3">
-        <v>1400</v>
+        <v>-12300</v>
       </c>
       <c r="J32" s="3">
-        <v>-900</v>
+        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>-600</v>
@@ -1702,22 +1702,22 @@
         <v>5000</v>
       </c>
       <c r="E33" s="3">
-        <v>-10600</v>
+        <v>-10900</v>
       </c>
       <c r="F33" s="3">
-        <v>-82000</v>
+        <v>-91600</v>
       </c>
       <c r="G33" s="3">
-        <v>68400</v>
+        <v>74400</v>
       </c>
       <c r="H33" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="I33" s="3">
-        <v>-124500</v>
+        <v>-127400</v>
       </c>
       <c r="J33" s="3">
-        <v>-86400</v>
+        <v>-94200</v>
       </c>
       <c r="K33" s="3">
         <v>-148500</v>
@@ -1786,22 +1786,22 @@
         <v>5000</v>
       </c>
       <c r="E35" s="3">
-        <v>-10600</v>
+        <v>-10900</v>
       </c>
       <c r="F35" s="3">
-        <v>-82000</v>
+        <v>-91600</v>
       </c>
       <c r="G35" s="3">
-        <v>68400</v>
+        <v>74400</v>
       </c>
       <c r="H35" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="I35" s="3">
-        <v>-124500</v>
+        <v>-127400</v>
       </c>
       <c r="J35" s="3">
-        <v>-86400</v>
+        <v>-94200</v>
       </c>
       <c r="K35" s="3">
         <v>-148500</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>626000</v>
+        <v>626200</v>
       </c>
       <c r="E41" s="3">
-        <v>569800</v>
+        <v>586000</v>
       </c>
       <c r="F41" s="3">
-        <v>628300</v>
+        <v>701500</v>
       </c>
       <c r="G41" s="3">
-        <v>744400</v>
+        <v>808700</v>
       </c>
       <c r="H41" s="3">
-        <v>1140800</v>
+        <v>1162200</v>
       </c>
       <c r="I41" s="3">
-        <v>784200</v>
+        <v>808700</v>
       </c>
       <c r="J41" s="3">
-        <v>76100</v>
+        <v>82900</v>
       </c>
       <c r="K41" s="3">
         <v>71800</v>
@@ -1950,25 +1950,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>242000</v>
+        <v>242100</v>
       </c>
       <c r="E42" s="3">
-        <v>354000</v>
+        <v>364100</v>
       </c>
       <c r="F42" s="3">
-        <v>292700</v>
+        <v>326900</v>
       </c>
       <c r="G42" s="3">
-        <v>314400</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>341600</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>61700</v>
+        <v>57700</v>
       </c>
       <c r="E43" s="3">
-        <v>65600</v>
+        <v>61300</v>
       </c>
       <c r="F43" s="3">
-        <v>77400</v>
+        <v>71000</v>
       </c>
       <c r="G43" s="3">
-        <v>59200</v>
+        <v>50300</v>
       </c>
       <c r="H43" s="3">
-        <v>56000</v>
+        <v>47100</v>
       </c>
       <c r="I43" s="3">
-        <v>53900</v>
+        <v>45400</v>
       </c>
       <c r="J43" s="3">
-        <v>32700</v>
+        <v>31100</v>
       </c>
       <c r="K43" s="3">
         <v>16300</v>
@@ -2033,26 +2033,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>12900</v>
+        <v>16900</v>
       </c>
       <c r="E45" s="3">
-        <v>8300</v>
+        <v>13900</v>
       </c>
       <c r="F45" s="3">
-        <v>20800</v>
+        <v>36900</v>
       </c>
       <c r="G45" s="3">
-        <v>14600</v>
+        <v>28100</v>
       </c>
       <c r="H45" s="3">
-        <v>15900</v>
+        <v>19900</v>
       </c>
       <c r="I45" s="3">
-        <v>24300</v>
+        <v>35300</v>
       </c>
       <c r="J45" s="3">
-        <v>12800</v>
+        <v>5500</v>
       </c>
       <c r="K45" s="3">
         <v>5800</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>942500</v>
+        <v>942800</v>
       </c>
       <c r="E46" s="3">
-        <v>997700</v>
+        <v>1026100</v>
       </c>
       <c r="F46" s="3">
-        <v>1019200</v>
+        <v>1138000</v>
       </c>
       <c r="G46" s="3">
-        <v>1132600</v>
+        <v>1230500</v>
       </c>
       <c r="H46" s="3">
-        <v>1212700</v>
+        <v>1235400</v>
       </c>
       <c r="I46" s="3">
-        <v>862400</v>
+        <v>889400</v>
       </c>
       <c r="J46" s="3">
-        <v>121600</v>
+        <v>132600</v>
       </c>
       <c r="K46" s="3">
         <v>94000</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>150300</v>
+        <v>150400</v>
       </c>
       <c r="E47" s="3">
-        <v>110200</v>
+        <v>113400</v>
       </c>
       <c r="F47" s="3">
-        <v>83400</v>
+        <v>93100</v>
       </c>
       <c r="G47" s="3">
-        <v>84700</v>
+        <v>92000</v>
       </c>
       <c r="H47" s="3">
-        <v>31800</v>
+        <v>32400</v>
       </c>
       <c r="I47" s="3">
-        <v>18900</v>
+        <v>19500</v>
       </c>
       <c r="J47" s="3">
-        <v>13600</v>
+        <v>14800</v>
       </c>
       <c r="K47" s="3">
         <v>4100</v>
@@ -2205,22 +2205,22 @@
         <v>5200</v>
       </c>
       <c r="E48" s="3">
-        <v>9400</v>
+        <v>9700</v>
       </c>
       <c r="F48" s="3">
-        <v>13700</v>
+        <v>15300</v>
       </c>
       <c r="G48" s="3">
-        <v>14100</v>
+        <v>15300</v>
       </c>
       <c r="H48" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="I48" s="3">
-        <v>7100</v>
+        <v>7300</v>
       </c>
       <c r="J48" s="3">
-        <v>7100</v>
+        <v>7700</v>
       </c>
       <c r="K48" s="3">
         <v>6900</v>
@@ -2247,22 +2247,22 @@
         <v>17000</v>
       </c>
       <c r="E49" s="3">
-        <v>17000</v>
+        <v>17500</v>
       </c>
       <c r="F49" s="3">
-        <v>24600</v>
+        <v>27400</v>
       </c>
       <c r="G49" s="3">
-        <v>21800</v>
+        <v>23700</v>
       </c>
       <c r="H49" s="3">
-        <v>32300</v>
+        <v>32900</v>
       </c>
       <c r="I49" s="3">
-        <v>20400</v>
+        <v>21000</v>
       </c>
       <c r="J49" s="3">
-        <v>2300</v>
+        <v>2600</v>
       </c>
       <c r="K49" s="3">
         <v>1600</v>
@@ -2373,22 +2373,22 @@
         <v>23000</v>
       </c>
       <c r="E52" s="3">
-        <v>13900</v>
+        <v>14300</v>
       </c>
       <c r="F52" s="3">
-        <v>9100</v>
+        <v>10200</v>
       </c>
       <c r="G52" s="3">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="H52" s="3">
         <v>1200</v>
       </c>
       <c r="I52" s="3">
-        <v>6800</v>
+        <v>7100</v>
       </c>
       <c r="J52" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K52" s="3">
         <v>1800</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1138000</v>
+        <v>1138400</v>
       </c>
       <c r="E54" s="3">
-        <v>1148300</v>
+        <v>1181000</v>
       </c>
       <c r="F54" s="3">
-        <v>1150000</v>
+        <v>1284000</v>
       </c>
       <c r="G54" s="3">
-        <v>1255800</v>
+        <v>1364500</v>
       </c>
       <c r="H54" s="3">
-        <v>1283400</v>
+        <v>1307500</v>
       </c>
       <c r="I54" s="3">
-        <v>915600</v>
+        <v>944300</v>
       </c>
       <c r="J54" s="3">
-        <v>145400</v>
+        <v>158500</v>
       </c>
       <c r="K54" s="3">
         <v>108300</v>
@@ -2532,25 +2532,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>75300</v>
+        <v>75400</v>
       </c>
       <c r="E57" s="3">
-        <v>94000</v>
+        <v>96700</v>
       </c>
       <c r="F57" s="3">
-        <v>116200</v>
+        <v>129700</v>
       </c>
       <c r="G57" s="3">
-        <v>139000</v>
+        <v>151000</v>
       </c>
       <c r="H57" s="3">
-        <v>125500</v>
+        <v>127800</v>
       </c>
       <c r="I57" s="3">
-        <v>112800</v>
+        <v>116400</v>
       </c>
       <c r="J57" s="3">
-        <v>63700</v>
+        <v>69500</v>
       </c>
       <c r="K57" s="3">
         <v>46700</v>
@@ -2574,16 +2574,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>118700</v>
+        <v>90600</v>
       </c>
       <c r="E59" s="3">
-        <v>125700</v>
+        <v>92800</v>
       </c>
       <c r="F59" s="3">
-        <v>144500</v>
+        <v>101800</v>
       </c>
       <c r="G59" s="3">
-        <v>126400</v>
+        <v>84500</v>
       </c>
       <c r="H59" s="3">
-        <v>127500</v>
+        <v>90200</v>
       </c>
       <c r="I59" s="3">
-        <v>290900</v>
+        <v>263600</v>
       </c>
       <c r="J59" s="3">
-        <v>59200</v>
+        <v>38900</v>
       </c>
       <c r="K59" s="3">
         <v>26100</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>194000</v>
+        <v>194100</v>
       </c>
       <c r="E60" s="3">
-        <v>219700</v>
+        <v>226000</v>
       </c>
       <c r="F60" s="3">
-        <v>260700</v>
+        <v>291100</v>
       </c>
       <c r="G60" s="3">
-        <v>265400</v>
+        <v>288400</v>
       </c>
       <c r="H60" s="3">
-        <v>253000</v>
+        <v>257700</v>
       </c>
       <c r="I60" s="3">
-        <v>403800</v>
+        <v>416400</v>
       </c>
       <c r="J60" s="3">
-        <v>122900</v>
+        <v>134000</v>
       </c>
       <c r="K60" s="3">
         <v>72800</v>
@@ -2700,16 +2700,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2741,20 +2741,20 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>900</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3700</v>
-      </c>
-      <c r="F62" s="3">
-        <v>7000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>6700</v>
-      </c>
-      <c r="H62" s="3">
-        <v>6500</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>194900</v>
+        <v>195000</v>
       </c>
       <c r="E66" s="3">
-        <v>223400</v>
+        <v>229800</v>
       </c>
       <c r="F66" s="3">
-        <v>267600</v>
+        <v>298800</v>
       </c>
       <c r="G66" s="3">
-        <v>277600</v>
+        <v>295700</v>
       </c>
       <c r="H66" s="3">
-        <v>262500</v>
+        <v>264300</v>
       </c>
       <c r="I66" s="3">
-        <v>403800</v>
+        <v>416400</v>
       </c>
       <c r="J66" s="3">
-        <v>122900</v>
+        <v>134000</v>
       </c>
       <c r="K66" s="3">
         <v>72800</v>
@@ -3069,10 +3069,10 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>936800</v>
+        <v>966100</v>
       </c>
       <c r="J70" s="3">
-        <v>370700</v>
+        <v>404100</v>
       </c>
       <c r="K70" s="3">
         <v>296000</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-491300</v>
+        <v>-491500</v>
       </c>
       <c r="E72" s="3">
-        <v>-496300</v>
+        <v>-510400</v>
       </c>
       <c r="F72" s="3">
-        <v>-485700</v>
+        <v>-542300</v>
       </c>
       <c r="G72" s="3">
-        <v>-403700</v>
+        <v>-438600</v>
       </c>
       <c r="H72" s="3">
-        <v>-472100</v>
+        <v>-480900</v>
       </c>
       <c r="I72" s="3">
-        <v>-477700</v>
+        <v>-492700</v>
       </c>
       <c r="J72" s="3">
-        <v>-354200</v>
+        <v>-386100</v>
       </c>
       <c r="K72" s="3">
         <v>-264000</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>943100</v>
+        <v>943400</v>
       </c>
       <c r="E76" s="3">
-        <v>924900</v>
+        <v>951200</v>
       </c>
       <c r="F76" s="3">
-        <v>882300</v>
+        <v>985200</v>
       </c>
       <c r="G76" s="3">
-        <v>978300</v>
+        <v>1062900</v>
       </c>
       <c r="H76" s="3">
-        <v>1021000</v>
+        <v>1040100</v>
       </c>
       <c r="I76" s="3">
-        <v>-424900</v>
+        <v>-438200</v>
       </c>
       <c r="J76" s="3">
-        <v>-348200</v>
+        <v>-379600</v>
       </c>
       <c r="K76" s="3">
         <v>-260500</v>
@@ -3440,22 +3440,22 @@
         <v>5000</v>
       </c>
       <c r="E81" s="3">
-        <v>-10600</v>
+        <v>-10900</v>
       </c>
       <c r="F81" s="3">
-        <v>-82000</v>
+        <v>-91600</v>
       </c>
       <c r="G81" s="3">
-        <v>68400</v>
+        <v>74400</v>
       </c>
       <c r="H81" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="I81" s="3">
-        <v>-124500</v>
+        <v>-127400</v>
       </c>
       <c r="J81" s="3">
-        <v>-86400</v>
+        <v>-94200</v>
       </c>
       <c r="K81" s="3">
         <v>-148500</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>13700</v>
+        <v>800</v>
       </c>
       <c r="E83" s="3">
-        <v>12300</v>
+        <v>1700</v>
       </c>
       <c r="F83" s="3">
-        <v>12500</v>
+        <v>2900</v>
       </c>
       <c r="G83" s="3">
-        <v>15600</v>
+        <v>3200</v>
       </c>
       <c r="H83" s="3">
-        <v>12700</v>
+        <v>4700</v>
       </c>
       <c r="I83" s="3">
-        <v>6400</v>
+        <v>3900</v>
       </c>
       <c r="J83" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="K83" s="3">
         <v>1000</v>
@@ -3752,22 +3752,22 @@
         <v>-6700</v>
       </c>
       <c r="E89" s="3">
-        <v>-9600</v>
+        <v>-9800</v>
       </c>
       <c r="F89" s="3">
-        <v>-82700</v>
+        <v>-92300</v>
       </c>
       <c r="G89" s="3">
-        <v>94100</v>
+        <v>102300</v>
       </c>
       <c r="H89" s="3">
-        <v>114600</v>
+        <v>116800</v>
       </c>
       <c r="I89" s="3">
-        <v>-47600</v>
+        <v>-49100</v>
       </c>
       <c r="J89" s="3">
-        <v>-53700</v>
+        <v>-58600</v>
       </c>
       <c r="K89" s="3">
         <v>-99300</v>
@@ -3818,16 +3818,16 @@
         <v>-1000</v>
       </c>
       <c r="G91" s="3">
-        <v>-2700</v>
+        <v>-2900</v>
       </c>
       <c r="H91" s="3">
         <v>-2300</v>
       </c>
       <c r="I91" s="3">
-        <v>-4600</v>
+        <v>-4800</v>
       </c>
       <c r="J91" s="3">
-        <v>-3400</v>
+        <v>-3700</v>
       </c>
       <c r="K91" s="3">
         <v>-6200</v>
@@ -3938,22 +3938,22 @@
         <v>58400</v>
       </c>
       <c r="E94" s="3">
-        <v>-85800</v>
+        <v>-88200</v>
       </c>
       <c r="F94" s="3">
-        <v>-2700</v>
+        <v>-3000</v>
       </c>
       <c r="G94" s="3">
-        <v>-368300</v>
+        <v>-400200</v>
       </c>
       <c r="H94" s="3">
-        <v>-34700</v>
+        <v>-35400</v>
       </c>
       <c r="I94" s="3">
-        <v>-37400</v>
+        <v>-38500</v>
       </c>
       <c r="J94" s="3">
-        <v>-13000</v>
+        <v>-14100</v>
       </c>
       <c r="K94" s="3">
         <v>-12000</v>
@@ -4166,22 +4166,22 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>-15400</v>
+        <v>-15800</v>
       </c>
       <c r="F100" s="3">
-        <v>-15100</v>
+        <v>-16900</v>
       </c>
       <c r="G100" s="3">
-        <v>-67600</v>
+        <v>-73400</v>
       </c>
       <c r="H100" s="3">
-        <v>267300</v>
+        <v>272300</v>
       </c>
       <c r="I100" s="3">
-        <v>744400</v>
+        <v>767700</v>
       </c>
       <c r="J100" s="3">
-        <v>70500</v>
+        <v>76800</v>
       </c>
       <c r="K100" s="3">
         <v>180500</v>
@@ -4208,19 +4208,19 @@
         <v>13400</v>
       </c>
       <c r="E101" s="3">
-        <v>51600</v>
+        <v>53100</v>
       </c>
       <c r="F101" s="3">
-        <v>-15800</v>
+        <v>-17700</v>
       </c>
       <c r="G101" s="3">
-        <v>-59100</v>
+        <v>-64200</v>
       </c>
       <c r="H101" s="3">
-        <v>15400</v>
+        <v>15700</v>
       </c>
       <c r="I101" s="3">
-        <v>48600</v>
+        <v>50200</v>
       </c>
       <c r="J101" s="3">
         <v>-600</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>65000</v>
+        <v>65100</v>
       </c>
       <c r="E102" s="3">
-        <v>-59100</v>
+        <v>-60800</v>
       </c>
       <c r="F102" s="3">
-        <v>-116300</v>
+        <v>-129800</v>
       </c>
       <c r="G102" s="3">
-        <v>-400800</v>
+        <v>-435500</v>
       </c>
       <c r="H102" s="3">
-        <v>362700</v>
+        <v>369500</v>
       </c>
       <c r="I102" s="3">
-        <v>708100</v>
+        <v>730300</v>
       </c>
       <c r="J102" s="3">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="K102" s="3">
         <v>69400</v>

--- a/AAII_Financials/Yearly/DOYU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOYU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>DOYU</t>
   </si>
@@ -656,58 +656,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -717,39 +717,42 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>585100</v>
+      </c>
+      <c r="E8" s="3">
         <v>779900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1030600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1442800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1470700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1046000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>531300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>289800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>109400</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -759,39 +762,42 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>540800</v>
+      </c>
+      <c r="E9" s="3">
         <v>683500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>887000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1271200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1231700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>874200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>509400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>290500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>160600</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,39 +807,42 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E10" s="3">
         <v>96500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>143600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>171600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>239000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>171800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-51200</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,38 +874,39 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E12" s="3">
         <v>35500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>49600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>69500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>55800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>55100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>47900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>32600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13000</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,38 +961,41 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>9700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>11900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>600</v>
-      </c>
-      <c r="H14" s="3">
-        <v>2700</v>
       </c>
       <c r="I14" s="3">
         <v>2700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
@@ -987,36 +1006,39 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E15" s="3">
         <v>13700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>17000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,38 +1070,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>662400</v>
+      </c>
+      <c r="E17" s="3">
         <v>800800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1059200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1544900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1430600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1064900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>656200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>384900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>217300</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,39 +1112,42 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-77300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-20900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-28600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-102100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>40100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-18900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-124900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-95000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-107900</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1128,9 +1157,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,38 +1179,39 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E20" s="3">
         <v>4400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1188,39 +1221,42 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-61400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-11600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-90500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>57300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-130500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-91200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-106300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,9 +1266,12 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1257,12 +1296,12 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>1200</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1272,39 +1311,42 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-38600</v>
+      </c>
+      <c r="E23" s="3">
         <v>5200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-97600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>62000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-127400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-94200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-108500</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,21 +1356,24 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1341,8 +1386,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1356,9 +1401,12 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,39 +1446,42 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="E26" s="3">
         <v>5000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-97600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>62000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-127400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-94200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-108500</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,39 +1491,42 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="E27" s="3">
         <v>5000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-91600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>74400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-128400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-94200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-148500</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,9 +1536,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,39 +1716,42 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1692,39 +1761,42 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="E33" s="3">
         <v>5000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-91600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>74400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-127400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-94200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-148500</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,9 +1806,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,39 +1851,42 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="E35" s="3">
         <v>5000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-91600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>74400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-127400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-94200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-148500</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,44 +1896,47 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1865,9 +1946,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,38 +1987,39 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>139400</v>
+      </c>
+      <c r="E41" s="3">
         <v>626200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>586000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>701500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>808700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1162200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>808700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>82900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>71800</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,41 +2029,44 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>420700</v>
+      </c>
+      <c r="E42" s="3">
         <v>242100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>364100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>326900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>341600</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -1985,39 +2074,42 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E43" s="3">
         <v>57700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>61300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>71000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>50300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>47100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>45400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>31100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16300</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,9 +2119,12 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2054,8 +2149,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2069,39 +2164,42 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E45" s="3">
         <v>16900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>36900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>28100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>19900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>35300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5800</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2111,39 +2209,42 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>612300</v>
+      </c>
+      <c r="E46" s="3">
         <v>942800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1026100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1138000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1230500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1235400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>889400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>132600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>94000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2153,39 +2254,42 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E47" s="3">
         <v>150400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>113400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>93100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>92000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>32400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>19500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>14800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2195,39 +2299,42 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E48" s="3">
         <v>5200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9700</v>
-      </c>
-      <c r="F48" s="3">
-        <v>15300</v>
       </c>
       <c r="G48" s="3">
         <v>15300</v>
       </c>
       <c r="H48" s="3">
+        <v>15300</v>
+      </c>
+      <c r="I48" s="3">
         <v>5600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6900</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,39 +2344,42 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E49" s="3">
         <v>17000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>27400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>32900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>21000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1600</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,39 +2479,42 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E52" s="3">
         <v>23000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1800</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2405,9 +2524,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,39 +2569,42 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>746200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1138400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1181000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1284000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1364500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1307500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>944300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>158500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>108300</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,9 +2614,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,38 +2655,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>68300</v>
+      </c>
+      <c r="E57" s="3">
         <v>75400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>96700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>129700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>151000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>127800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>116400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>69500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>46700</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,27 +2697,30 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E58" s="3">
         <v>2100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5600</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -2609,39 +2742,42 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>65700</v>
+      </c>
+      <c r="E59" s="3">
         <v>90600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>92800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>101800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>84500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>90200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>263600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>38900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>26100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2651,39 +2787,42 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>167500</v>
+      </c>
+      <c r="E60" s="3">
         <v>194100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>226000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>291100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>288400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>257700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>416400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>134000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>72800</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,27 +2832,30 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>600</v>
+      </c>
+      <c r="E61" s="3">
         <v>900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2600</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2735,9 +2877,12 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2774,12 +2919,15 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,39 +3057,42 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>168100</v>
+      </c>
+      <c r="E66" s="3">
         <v>195000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>229800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>298800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>295700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>264300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>416400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>134000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>72800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2945,9 +3102,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3069,17 +3236,17 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>966100</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>404100</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>296000</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,39 +3301,42 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-518200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-491500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-510400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-542300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-438600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-480900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-492700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-386100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-264000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,9 +3346,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,39 +3481,42 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>578100</v>
+      </c>
+      <c r="E76" s="3">
         <v>943400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>951200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>985200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1062900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1040100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-438200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-379600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-260500</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,9 +3526,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,44 +3571,47 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3430,39 +3621,42 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="E81" s="3">
         <v>5000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-91600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>74400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-127400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-94200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-148500</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,9 +3666,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,38 +3688,39 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,9 +3730,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,39 +3955,42 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-92300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>102300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>116800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-49100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-58600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-99300</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3784,9 +4000,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,38 +4022,39 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6200</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,9 +4064,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,39 +4154,42 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>58400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-88200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-400200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-35400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-38500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3970,9 +4199,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4221,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,39 +4398,42 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-15800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-16900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-73400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>272300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>767700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>76800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>180500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,39 +4443,42 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3">
         <v>13400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>53100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-17700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-64200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>15700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>50200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4240,39 +4488,42 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>65100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-60800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-129800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-435500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>369500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>730300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>69400</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,7 +4533,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/DOYU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOYU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>DOYU</t>
   </si>
@@ -881,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>24900</v>
+        <v>22700</v>
       </c>
       <c r="E12" s="3">
         <v>35500</v>
@@ -970,8 +970,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>5500</v>
       </c>
       <c r="E14" s="3">
         <v>9700</v>
@@ -1016,7 +1016,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>13300</v>
+        <v>8600</v>
       </c>
       <c r="E15" s="3">
         <v>13700</v>
@@ -1077,7 +1077,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>662400</v>
+        <v>655200</v>
       </c>
       <c r="E17" s="3">
         <v>800800</v>
@@ -1122,7 +1122,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-77300</v>
+        <v>-70100</v>
       </c>
       <c r="E18" s="3">
         <v>-20900</v>
@@ -1186,7 +1186,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2600</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
         <v>4400</v>
@@ -1231,7 +1231,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-61400</v>
+        <v>-61900</v>
       </c>
       <c r="E21" s="3">
         <v>-11600</v>
@@ -1321,7 +1321,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-38600</v>
+        <v>-39900</v>
       </c>
       <c r="E23" s="3">
         <v>5200</v>
@@ -1456,7 +1456,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-40800</v>
+        <v>-42000</v>
       </c>
       <c r="E26" s="3">
         <v>5000</v>
@@ -1501,7 +1501,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-40800</v>
+        <v>-42000</v>
       </c>
       <c r="E27" s="3">
         <v>5000</v>
@@ -1726,7 +1726,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2600</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
         <v>-4400</v>
@@ -1771,7 +1771,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-40800</v>
+        <v>-42000</v>
       </c>
       <c r="E33" s="3">
         <v>5000</v>
@@ -1861,7 +1861,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-40800</v>
+        <v>-42000</v>
       </c>
       <c r="E35" s="3">
         <v>5000</v>
@@ -2084,7 +2084,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>16900</v>
+        <v>43100</v>
       </c>
       <c r="E43" s="3">
         <v>57700</v>
@@ -2174,7 +2174,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>35400</v>
+        <v>9200</v>
       </c>
       <c r="E45" s="3">
         <v>16900</v>
@@ -2752,7 +2752,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>65700</v>
+        <v>75100</v>
       </c>
       <c r="E59" s="3">
         <v>90600</v>
@@ -2797,7 +2797,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>167500</v>
+        <v>168800</v>
       </c>
       <c r="E60" s="3">
         <v>194100</v>
@@ -3067,7 +3067,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>168100</v>
+        <v>169400</v>
       </c>
       <c r="E66" s="3">
         <v>195000</v>
@@ -3311,7 +3311,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-518200</v>
+        <v>-519500</v>
       </c>
       <c r="E72" s="3">
         <v>-491500</v>
@@ -3491,7 +3491,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>578100</v>
+        <v>576800</v>
       </c>
       <c r="E76" s="3">
         <v>943400</v>
@@ -3631,7 +3631,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-40800</v>
+        <v>-42000</v>
       </c>
       <c r="E81" s="3">
         <v>5000</v>
@@ -3694,8 +3694,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>900</v>
       </c>
       <c r="E83" s="3">
         <v>800</v>
@@ -3964,8 +3964,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-32700</v>
       </c>
       <c r="E89" s="3">
         <v>-6700</v>
@@ -4028,14 +4028,14 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>-700</v>
       </c>
       <c r="F91" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="G91" s="3">
         <v>-1000</v>
@@ -4163,8 +4163,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-147200</v>
       </c>
       <c r="E94" s="3">
         <v>58400</v>
@@ -4228,7 +4228,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>287900</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -4407,8 +4407,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>-302400</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -4452,8 +4452,8 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>6700</v>
       </c>
       <c r="E101" s="3">
         <v>13400</v>
@@ -4498,7 +4498,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-475600</v>
       </c>
       <c r="E102" s="3">
         <v>65100</v>

--- a/AAII_Financials/Yearly/DOYU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOYU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>DOYU</t>
   </si>
@@ -656,61 +656,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -720,42 +720,45 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>546000</v>
+      </c>
+      <c r="E8" s="3">
         <v>585100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>779900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1030600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1442800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1470700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1046000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>531300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>289800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>109400</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,42 +768,45 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>476000</v>
+      </c>
+      <c r="E9" s="3">
         <v>540800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>683500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>887000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1271200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1231700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>874200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>509400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>290500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>160600</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,42 +816,45 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E10" s="3">
         <v>44400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>96500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>143600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>171600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>239000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>171800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-51200</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,41 +887,42 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E12" s="3">
         <v>22700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>35500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>49600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>69500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>55800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>55100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>47900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>32600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13000</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,41 +980,44 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>5500</v>
+        <v>9600</v>
       </c>
       <c r="E14" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F14" s="3">
         <v>9700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>11900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>600</v>
-      </c>
-      <c r="I14" s="3">
-        <v>2700</v>
       </c>
       <c r="J14" s="3">
         <v>2700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
@@ -1009,39 +1028,42 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E15" s="3">
         <v>8600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>12700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,41 +1096,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>655200</v>
+        <v>545300</v>
       </c>
       <c r="E17" s="3">
+        <v>663600</v>
+      </c>
+      <c r="F17" s="3">
         <v>800800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1059200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1544900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1430600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1064900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>656200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>384900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>217300</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1115,42 +1141,45 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-70100</v>
+        <v>700</v>
       </c>
       <c r="E18" s="3">
+        <v>-78500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-20900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-28600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-102100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>40100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-18900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-124900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-95000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-107900</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1160,9 +1189,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,41 +1212,42 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-9000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>12300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1224,42 +1257,45 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-61900</v>
+        <v>4900</v>
       </c>
       <c r="E21" s="3">
+        <v>-70300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-11600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-90500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>57300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-130500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-91200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-106300</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,9 +1305,12 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1299,12 +1338,12 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
         <v>1200</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,42 +1353,45 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-39900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-97600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>62000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-127400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-94200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-108500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,24 +1401,27 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E24" s="3">
         <v>2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1389,8 +1434,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1404,9 +1449,12 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,42 +1497,45 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-42000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-97600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>62000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-127400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-94200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-108500</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1494,42 +1545,45 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-42000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-91600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>74400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-128400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-94200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-148500</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,9 +1593,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,42 +1785,45 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>9000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-12300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1764,42 +1833,45 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-42000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-91600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>74400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-127400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-94200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-148500</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,9 +1881,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,42 +1929,45 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-42000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-91600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>74400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-127400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-94200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-148500</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1899,47 +1977,50 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1949,9 +2030,12 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,41 +2073,42 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>251500</v>
+      </c>
+      <c r="E41" s="3">
         <v>139400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>626200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>586000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>701500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>808700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1162200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>808700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>82900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>71800</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2032,44 +2118,47 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E42" s="3">
         <v>420700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>242100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>364100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>326900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>341600</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2077,42 +2166,45 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E43" s="3">
         <v>43100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>57700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>61300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>71000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>50300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>47100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>45400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>31100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16300</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,9 +2214,12 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2152,8 +2247,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2167,42 +2262,45 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E45" s="3">
         <v>9200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>36900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>19900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>35300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5800</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2212,42 +2310,45 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>376300</v>
+      </c>
+      <c r="E46" s="3">
         <v>612300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>942800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1026100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1138000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1230500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1235400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>889400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>132600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>94000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2257,42 +2358,45 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E47" s="3">
         <v>111900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>150400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>113400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>93100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>92000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>32400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>19500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>14800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,42 +2406,45 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E48" s="3">
         <v>3100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9700</v>
-      </c>
-      <c r="G48" s="3">
-        <v>15300</v>
       </c>
       <c r="H48" s="3">
         <v>15300</v>
       </c>
       <c r="I48" s="3">
+        <v>15300</v>
+      </c>
+      <c r="J48" s="3">
         <v>5600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6900</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2347,42 +2454,45 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E49" s="3">
         <v>8300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>27400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>32900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>21000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1600</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,42 +2598,45 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E52" s="3">
         <v>10500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>23000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1800</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2527,9 +2646,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,42 +2694,45 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>446100</v>
+      </c>
+      <c r="E54" s="3">
         <v>746200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1138400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1181000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1284000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1364500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1307500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>944300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>158500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>108300</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2617,9 +2742,12 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,41 +2785,42 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>79200</v>
+      </c>
+      <c r="E57" s="3">
         <v>68300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>75400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>96700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>129700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>151000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>127800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>116400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>69500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>46700</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,30 +2830,33 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5600</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -2745,42 +2878,45 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E59" s="3">
         <v>75100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>90600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>92800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>101800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>84500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>90200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>263600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>38900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>26100</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,42 +2926,45 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>161700</v>
+      </c>
+      <c r="E60" s="3">
         <v>168800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>194100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>226000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>291100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>288400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>257700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>416400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>134000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>72800</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,30 +2974,33 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>200</v>
+      </c>
+      <c r="E61" s="3">
         <v>600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2600</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2880,9 +3022,12 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2922,12 +3067,15 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,42 +3214,45 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>161900</v>
+      </c>
+      <c r="E66" s="3">
         <v>169400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>195000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>229800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>298800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>295700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>264300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>416400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>134000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>72800</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,9 +3262,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3239,17 +3406,17 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>966100</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>404100</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>296000</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,42 +3474,45 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-546300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-519500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-491500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-510400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-542300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-438600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-480900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-492700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-386100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-264000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,9 +3522,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,42 +3666,45 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>284100</v>
+      </c>
+      <c r="E76" s="3">
         <v>576800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>943400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>951200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>985200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1062900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1040100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-438200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-379600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-260500</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3529,9 +3714,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,47 +3762,50 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3624,42 +3815,45 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-42000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-91600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>74400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-127400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-94200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-148500</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3669,9 +3863,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,41 +3886,42 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3">
         <v>900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3733,9 +3931,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,42 +4171,45 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-92300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>102300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>116800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-49100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-58600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-99300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,9 +4219,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,41 +4242,42 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6200</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,9 +4287,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,42 +4383,45 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>424900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-147200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>58400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-88200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-400200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-35400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-38500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4202,9 +4431,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,17 +4454,18 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>307500</v>
+      </c>
+      <c r="E96" s="3">
         <v>287900</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,42 +4643,45 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-307500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-302400</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-15800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-16900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-73400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>272300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>767700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>76800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>180500</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4446,42 +4691,45 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E101" s="3">
         <v>6700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>13400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>53100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-17700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-64200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>15700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>50200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4491,42 +4739,45 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>106300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-475600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>65100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-60800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-129800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-435500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>369500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>730300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>69400</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4536,7 +4787,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
